--- a/output7/【河洛文讀注音-方音符號】《蘭亭集序》.xlsx
+++ b/output7/【河洛文讀注音-方音符號】《蘭亭集序》.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A075E0E-9D3A-434E-920E-3A7F07DA6BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201A071B-7E99-475D-8338-F1F505E2CCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38670" yWindow="-75" windowWidth="28635" windowHeight="15585" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5120" uniqueCount="2408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5120" uniqueCount="2412">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -8279,6 +8279,22 @@
   </si>
   <si>
     <t>(113, 7); (113, 11); (117, 7); (117, 11)</t>
+  </si>
+  <si>
+    <t>漢字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台語音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>校正音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>座標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8746,7 +8762,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8934,7 +8950,13 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8943,29 +8965,14 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -12408,7 +12415,7 @@
       <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="63" t="s">
         <v>1893</v>
       </c>
     </row>
@@ -12416,7 +12423,7 @@
       <c r="B9" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="49" t="s">
         <v>1894</v>
       </c>
     </row>
@@ -12424,7 +12431,7 @@
       <c r="B10" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="70" t="b">
+      <c r="C10" s="49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -12432,7 +12439,7 @@
       <c r="B11" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="70">
+      <c r="C11" s="49">
         <v>120</v>
       </c>
     </row>
@@ -12440,7 +12447,7 @@
       <c r="B12" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="70">
+      <c r="C12" s="49">
         <v>15</v>
       </c>
     </row>
@@ -12448,7 +12455,7 @@
       <c r="B13" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="62" t="s">
         <v>1544</v>
       </c>
     </row>
@@ -12456,7 +12463,7 @@
       <c r="B14" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="62" t="s">
         <v>1895</v>
       </c>
     </row>
@@ -12464,7 +12471,7 @@
       <c r="B15" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="69" t="s">
+      <c r="C15" s="62" t="s">
         <v>1896</v>
       </c>
     </row>
@@ -12472,7 +12479,7 @@
       <c r="B16" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="62" t="s">
         <v>1897</v>
       </c>
     </row>
@@ -12480,7 +12487,7 @@
       <c r="B17" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="62" t="s">
         <v>1898</v>
       </c>
     </row>
@@ -12488,7 +12495,7 @@
       <c r="B18" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="69" t="s">
+      <c r="C18" s="62" t="s">
         <v>1896</v>
       </c>
     </row>
@@ -12496,7 +12503,7 @@
       <c r="B19" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="69" t="s">
+      <c r="C19" s="62" t="s">
         <v>1797</v>
       </c>
     </row>
@@ -12544,16 +12551,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>2408</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>2409</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>2410</v>
       </c>
       <c r="D1" t="s">
-        <v>498</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -16601,16 +16608,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>2408</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>2409</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>2410</v>
       </c>
       <c r="D1" t="s">
-        <v>498</v>
+        <v>2411</v>
       </c>
     </row>
   </sheetData>
@@ -16626,16 +16633,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>2408</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>2409</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>2410</v>
       </c>
       <c r="D1" t="s">
-        <v>498</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -17716,7 +17723,7 @@
       <c r="Q3" s="60"/>
       <c r="R3" s="60"/>
       <c r="T3" s="16"/>
-      <c r="V3" s="68" t="s">
+      <c r="V3" s="64" t="s">
         <v>1899</v>
       </c>
     </row>
@@ -17746,36 +17753,36 @@
       <c r="Q4" s="61"/>
       <c r="R4" s="61"/>
       <c r="S4" s="19"/>
-      <c r="V4" s="63"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="20">
         <v>1</v>
       </c>
-      <c r="D5" s="72" t="s">
+      <c r="D5" s="41" t="s">
         <v>1900</v>
       </c>
-      <c r="E5" s="72" t="s">
+      <c r="E5" s="41" t="s">
         <v>1602</v>
       </c>
-      <c r="F5" s="72" t="s">
+      <c r="F5" s="41" t="s">
         <v>1603</v>
       </c>
-      <c r="G5" s="72" t="s">
+      <c r="G5" s="41" t="s">
         <v>1616</v>
       </c>
-      <c r="H5" s="72" t="s">
+      <c r="H5" s="41" t="s">
         <v>1903</v>
       </c>
-      <c r="I5" s="72" t="s">
+      <c r="I5" s="41" t="s">
         <v>1901</v>
       </c>
-      <c r="J5" s="72" t="str">
+      <c r="J5" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="K5" s="72"/>
+      <c r="K5" s="41"/>
       <c r="L5" s="41"/>
       <c r="M5" s="41"/>
       <c r="N5" s="41"/>
@@ -17784,7 +17791,7 @@
       <c r="Q5" s="41"/>
       <c r="R5" s="41"/>
       <c r="S5" s="21"/>
-      <c r="V5" s="63"/>
+      <c r="V5" s="65"/>
     </row>
     <row r="6" spans="1:22" s="26" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="22"/>
@@ -17813,7 +17820,7 @@
       <c r="Q6" s="24"/>
       <c r="R6" s="24"/>
       <c r="S6" s="25"/>
-      <c r="V6" s="63"/>
+      <c r="V6" s="65"/>
     </row>
     <row r="7" spans="1:22" s="30" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="27"/>
@@ -17842,7 +17849,7 @@
       <c r="Q7" s="54"/>
       <c r="R7" s="54"/>
       <c r="S7" s="29"/>
-      <c r="V7" s="63"/>
+      <c r="V7" s="65"/>
     </row>
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="17"/>
@@ -17886,61 +17893,61 @@
       </c>
       <c r="R8" s="18"/>
       <c r="S8" s="19"/>
-      <c r="V8" s="63"/>
+      <c r="V8" s="65"/>
     </row>
     <row r="9" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="20">
         <f>B5+1</f>
         <v>2</v>
       </c>
-      <c r="D9" s="72" t="s">
+      <c r="D9" s="41" t="s">
         <v>1584</v>
       </c>
-      <c r="E9" s="72" t="s">
+      <c r="E9" s="41" t="s">
         <v>1585</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="F9" s="41" t="s">
         <v>1586</v>
       </c>
-      <c r="G9" s="72" t="s">
+      <c r="G9" s="41" t="s">
         <v>1587</v>
       </c>
-      <c r="H9" s="72" t="s">
+      <c r="H9" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="I9" s="72" t="s">
+      <c r="I9" s="41" t="s">
         <v>1589</v>
       </c>
-      <c r="J9" s="72" t="s">
+      <c r="J9" s="41" t="s">
         <v>1590</v>
       </c>
-      <c r="K9" s="72" t="s">
+      <c r="K9" s="41" t="s">
         <v>1591</v>
       </c>
-      <c r="L9" s="72" t="s">
+      <c r="L9" s="41" t="s">
         <v>1592</v>
       </c>
-      <c r="M9" s="72" t="s">
+      <c r="M9" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="N9" s="72" t="s">
+      <c r="N9" s="41" t="s">
         <v>1593</v>
       </c>
-      <c r="O9" s="72" t="s">
+      <c r="O9" s="41" t="s">
         <v>1594</v>
       </c>
-      <c r="P9" s="72" t="s">
+      <c r="P9" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="Q9" s="72" t="s">
+      <c r="Q9" s="41" t="s">
         <v>1596</v>
       </c>
-      <c r="R9" s="72" t="s">
+      <c r="R9" s="41" t="s">
         <v>1588</v>
       </c>
       <c r="S9" s="21"/>
       <c r="T9" s="16"/>
-      <c r="V9" s="63"/>
+      <c r="V9" s="65"/>
     </row>
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="22"/>
@@ -17984,7 +17991,7 @@
       </c>
       <c r="R10" s="24"/>
       <c r="S10" s="31"/>
-      <c r="V10" s="63"/>
+      <c r="V10" s="65"/>
     </row>
     <row r="11" spans="1:22" s="29" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="32"/>
@@ -18020,7 +18027,7 @@
         <v>2287</v>
       </c>
       <c r="R11" s="54"/>
-      <c r="V11" s="63"/>
+      <c r="V11" s="65"/>
     </row>
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="17"/>
@@ -18066,60 +18073,60 @@
       </c>
       <c r="R12" s="18"/>
       <c r="S12" s="19"/>
-      <c r="V12" s="63"/>
+      <c r="V12" s="65"/>
     </row>
     <row r="13" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="20">
         <f>B9+1</f>
         <v>3</v>
       </c>
-      <c r="D13" s="72" t="s">
+      <c r="D13" s="41" t="s">
         <v>1597</v>
       </c>
-      <c r="E13" s="72" t="s">
+      <c r="E13" s="41" t="s">
         <v>1598</v>
       </c>
-      <c r="F13" s="72" t="s">
+      <c r="F13" s="41" t="s">
         <v>1597</v>
       </c>
-      <c r="G13" s="72" t="s">
+      <c r="G13" s="41" t="s">
         <v>1599</v>
       </c>
-      <c r="H13" s="72" t="s">
+      <c r="H13" s="41" t="s">
         <v>1600</v>
       </c>
-      <c r="I13" s="72" t="s">
+      <c r="I13" s="41" t="s">
         <v>1601</v>
       </c>
-      <c r="J13" s="72" t="s">
+      <c r="J13" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="K13" s="72" t="s">
+      <c r="K13" s="41" t="s">
         <v>1602</v>
       </c>
-      <c r="L13" s="72" t="s">
+      <c r="L13" s="41" t="s">
         <v>1603</v>
       </c>
-      <c r="M13" s="72" t="s">
+      <c r="M13" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="N13" s="72" t="s">
+      <c r="N13" s="41" t="s">
         <v>1604</v>
       </c>
-      <c r="O13" s="72" t="s">
+      <c r="O13" s="41" t="s">
         <v>1605</v>
       </c>
-      <c r="P13" s="72" t="s">
+      <c r="P13" s="41" t="s">
         <v>1606</v>
       </c>
-      <c r="Q13" s="72" t="s">
+      <c r="Q13" s="41" t="s">
         <v>1607</v>
       </c>
-      <c r="R13" s="72" t="s">
+      <c r="R13" s="41" t="s">
         <v>1608</v>
       </c>
       <c r="S13" s="21"/>
-      <c r="V13" s="63"/>
+      <c r="V13" s="65"/>
     </row>
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="22"/>
@@ -18165,7 +18172,7 @@
       </c>
       <c r="R14" s="24"/>
       <c r="S14" s="31"/>
-      <c r="V14" s="63"/>
+      <c r="V14" s="65"/>
     </row>
     <row r="15" spans="1:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="12"/>
@@ -18195,7 +18202,7 @@
       <c r="R15" s="54" t="s">
         <v>2281</v>
       </c>
-      <c r="V15" s="63"/>
+      <c r="V15" s="65"/>
     </row>
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="17"/>
@@ -18241,60 +18248,60 @@
         <v>623</v>
       </c>
       <c r="S16" s="19"/>
-      <c r="V16" s="63"/>
+      <c r="V16" s="65"/>
     </row>
     <row r="17" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="20">
         <f>B13+1</f>
         <v>4</v>
       </c>
-      <c r="D17" s="72" t="s">
+      <c r="D17" s="41" t="s">
         <v>1609</v>
       </c>
-      <c r="E17" s="72" t="s">
+      <c r="E17" s="41" t="s">
         <v>1610</v>
       </c>
-      <c r="F17" s="72" t="s">
+      <c r="F17" s="41" t="s">
         <v>1611</v>
       </c>
-      <c r="G17" s="72" t="s">
+      <c r="G17" s="41" t="s">
         <v>1612</v>
       </c>
-      <c r="H17" s="72" t="s">
+      <c r="H17" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="I17" s="72" t="s">
+      <c r="I17" s="41" t="s">
         <v>1613</v>
       </c>
-      <c r="J17" s="72" t="s">
+      <c r="J17" s="41" t="s">
         <v>1614</v>
       </c>
-      <c r="K17" s="72" t="s">
+      <c r="K17" s="41" t="s">
         <v>1615</v>
       </c>
-      <c r="L17" s="72" t="s">
+      <c r="L17" s="41" t="s">
         <v>1616</v>
       </c>
-      <c r="M17" s="72" t="s">
+      <c r="M17" s="41" t="s">
         <v>1608</v>
       </c>
-      <c r="N17" s="72" t="s">
+      <c r="N17" s="41" t="s">
         <v>1617</v>
       </c>
-      <c r="O17" s="72" t="s">
+      <c r="O17" s="41" t="s">
         <v>1618</v>
       </c>
-      <c r="P17" s="72" t="s">
+      <c r="P17" s="41" t="s">
         <v>1619</v>
       </c>
-      <c r="Q17" s="72" t="s">
+      <c r="Q17" s="41" t="s">
         <v>1620</v>
       </c>
-      <c r="R17" s="72" t="s">
+      <c r="R17" s="41" t="s">
         <v>1600</v>
       </c>
       <c r="S17" s="21"/>
-      <c r="V17" s="63"/>
+      <c r="V17" s="65"/>
     </row>
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="22"/>
@@ -18340,7 +18347,7 @@
         <v>2302</v>
       </c>
       <c r="S18" s="31"/>
-      <c r="V18" s="63"/>
+      <c r="V18" s="65"/>
     </row>
     <row r="19" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="12"/>
@@ -18370,7 +18377,7 @@
       <c r="P19" s="54"/>
       <c r="Q19" s="54"/>
       <c r="R19" s="54"/>
-      <c r="V19" s="63"/>
+      <c r="V19" s="65"/>
     </row>
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="17"/>
@@ -18414,60 +18421,60 @@
       </c>
       <c r="R20" s="18"/>
       <c r="S20" s="19"/>
-      <c r="V20" s="63"/>
+      <c r="V20" s="65"/>
     </row>
     <row r="21" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="20">
         <f>B17+1</f>
         <v>5</v>
       </c>
-      <c r="D21" s="72" t="s">
+      <c r="D21" s="41" t="s">
         <v>1621</v>
       </c>
-      <c r="E21" s="72" t="s">
+      <c r="E21" s="41" t="s">
         <v>1622</v>
       </c>
-      <c r="F21" s="72" t="s">
+      <c r="F21" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="G21" s="72" t="s">
+      <c r="G21" s="41" t="s">
         <v>1623</v>
       </c>
-      <c r="H21" s="72" t="s">
+      <c r="H21" s="41" t="s">
         <v>1624</v>
       </c>
-      <c r="I21" s="72" t="s">
+      <c r="I21" s="41" t="s">
         <v>1604</v>
       </c>
-      <c r="J21" s="72" t="s">
+      <c r="J21" s="41" t="s">
         <v>1625</v>
       </c>
-      <c r="K21" s="72" t="s">
+      <c r="K21" s="41" t="s">
         <v>1626</v>
       </c>
-      <c r="L21" s="72" t="s">
+      <c r="L21" s="41" t="s">
         <v>1627</v>
       </c>
-      <c r="M21" s="72" t="s">
+      <c r="M21" s="41" t="s">
         <v>1619</v>
       </c>
-      <c r="N21" s="72" t="s">
+      <c r="N21" s="41" t="s">
         <v>1628</v>
       </c>
-      <c r="O21" s="72" t="s">
+      <c r="O21" s="41" t="s">
         <v>1629</v>
       </c>
-      <c r="P21" s="72" t="s">
+      <c r="P21" s="41" t="s">
         <v>1630</v>
       </c>
-      <c r="Q21" s="72" t="s">
+      <c r="Q21" s="41" t="s">
         <v>1631</v>
       </c>
-      <c r="R21" s="72" t="s">
+      <c r="R21" s="41" t="s">
         <v>1588</v>
       </c>
       <c r="S21" s="21"/>
-      <c r="V21" s="63"/>
+      <c r="V21" s="65"/>
     </row>
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="22"/>
@@ -18511,7 +18518,7 @@
       </c>
       <c r="R22" s="24"/>
       <c r="S22" s="31"/>
-      <c r="V22" s="63"/>
+      <c r="V22" s="65"/>
     </row>
     <row r="23" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="12"/>
@@ -18541,7 +18548,7 @@
       <c r="R23" s="54" t="s">
         <v>1823</v>
       </c>
-      <c r="V23" s="63"/>
+      <c r="V23" s="65"/>
     </row>
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="17"/>
@@ -18587,60 +18594,60 @@
         <v>1823</v>
       </c>
       <c r="S24" s="19"/>
-      <c r="V24" s="63"/>
+      <c r="V24" s="65"/>
     </row>
     <row r="25" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B25" s="20">
         <f>B21+1</f>
         <v>6</v>
       </c>
-      <c r="D25" s="72" t="s">
+      <c r="D25" s="41" t="s">
         <v>1632</v>
       </c>
-      <c r="E25" s="72" t="s">
+      <c r="E25" s="41" t="s">
         <v>1633</v>
       </c>
-      <c r="F25" s="72" t="s">
+      <c r="F25" s="41" t="s">
         <v>1634</v>
       </c>
-      <c r="G25" s="72" t="s">
+      <c r="G25" s="41" t="s">
         <v>1635</v>
       </c>
-      <c r="H25" s="72" t="s">
+      <c r="H25" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="I25" s="72" t="s">
+      <c r="I25" s="41" t="s">
         <v>1636</v>
       </c>
-      <c r="J25" s="72" t="s">
+      <c r="J25" s="41" t="s">
         <v>1637</v>
       </c>
-      <c r="K25" s="72" t="s">
+      <c r="K25" s="41" t="s">
         <v>1638</v>
       </c>
-      <c r="L25" s="72" t="s">
+      <c r="L25" s="41" t="s">
         <v>1629</v>
       </c>
-      <c r="M25" s="72" t="s">
+      <c r="M25" s="41" t="s">
         <v>1639</v>
       </c>
-      <c r="N25" s="72" t="s">
+      <c r="N25" s="41" t="s">
         <v>1640</v>
       </c>
-      <c r="O25" s="72" t="s">
+      <c r="O25" s="41" t="s">
         <v>1641</v>
       </c>
-      <c r="P25" s="72" t="s">
+      <c r="P25" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="Q25" s="72" t="s">
+      <c r="Q25" s="41" t="s">
         <v>1642</v>
       </c>
-      <c r="R25" s="72" t="s">
+      <c r="R25" s="41" t="s">
         <v>1643</v>
       </c>
       <c r="S25" s="21"/>
-      <c r="V25" s="63"/>
+      <c r="V25" s="65"/>
     </row>
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="22"/>
@@ -18686,7 +18693,7 @@
         <v>2312</v>
       </c>
       <c r="S26" s="31"/>
-      <c r="V26" s="63"/>
+      <c r="V26" s="65"/>
     </row>
     <row r="27" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B27" s="12"/>
@@ -18714,7 +18721,7 @@
         <f t="shared" ref="U27:U32" si="1" xml:space="preserve"> MID($N$30,4,1)</f>
         <v>n</v>
       </c>
-      <c r="V27" s="63"/>
+      <c r="V27" s="65"/>
     </row>
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="17"/>
@@ -18764,56 +18771,56 @@
         <f t="shared" si="1"/>
         <v>n</v>
       </c>
-      <c r="V28" s="63"/>
+      <c r="V28" s="65"/>
     </row>
     <row r="29" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B29" s="20">
         <f>B25+1</f>
         <v>7</v>
       </c>
-      <c r="D29" s="72" t="s">
+      <c r="D29" s="41" t="s">
         <v>1644</v>
       </c>
-      <c r="E29" s="72" t="s">
+      <c r="E29" s="41" t="s">
         <v>1645</v>
       </c>
-      <c r="F29" s="72" t="s">
+      <c r="F29" s="41" t="s">
         <v>1608</v>
       </c>
-      <c r="G29" s="72" t="s">
+      <c r="G29" s="41" t="s">
         <v>1646</v>
       </c>
-      <c r="H29" s="72" t="s">
+      <c r="H29" s="41" t="s">
         <v>1647</v>
       </c>
-      <c r="I29" s="72" t="s">
+      <c r="I29" s="41" t="s">
         <v>1648</v>
       </c>
-      <c r="J29" s="72" t="s">
+      <c r="J29" s="41" t="s">
         <v>1625</v>
       </c>
-      <c r="K29" s="72" t="s">
+      <c r="K29" s="41" t="s">
         <v>1649</v>
       </c>
-      <c r="L29" s="72" t="s">
+      <c r="L29" s="41" t="s">
         <v>1650</v>
       </c>
-      <c r="M29" s="72" t="s">
+      <c r="M29" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="N29" s="72" t="s">
+      <c r="N29" s="41" t="s">
         <v>1651</v>
       </c>
-      <c r="O29" s="72" t="s">
+      <c r="O29" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="P29" s="72" t="s">
+      <c r="P29" s="41" t="s">
         <v>1652</v>
       </c>
-      <c r="Q29" s="72" t="s">
+      <c r="Q29" s="41" t="s">
         <v>1639</v>
       </c>
-      <c r="R29" s="72" t="s">
+      <c r="R29" s="41" t="s">
         <v>1652</v>
       </c>
       <c r="S29" s="21"/>
@@ -18821,7 +18828,7 @@
         <f t="shared" si="1"/>
         <v>n</v>
       </c>
-      <c r="V29" s="63"/>
+      <c r="V29" s="65"/>
     </row>
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="22"/>
@@ -18871,7 +18878,7 @@
         <f t="shared" si="1"/>
         <v>n</v>
       </c>
-      <c r="V30" s="63"/>
+      <c r="V30" s="65"/>
     </row>
     <row r="31" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B31" s="12"/>
@@ -18897,7 +18904,7 @@
         <f t="shared" si="1"/>
         <v>n</v>
       </c>
-      <c r="V31" s="63"/>
+      <c r="V31" s="65"/>
     </row>
     <row r="32" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="17"/>
@@ -18937,44 +18944,44 @@
         <f t="shared" si="1"/>
         <v>n</v>
       </c>
-      <c r="V32" s="63"/>
+      <c r="V32" s="65"/>
     </row>
     <row r="33" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B33" s="20">
         <f>B29+1</f>
         <v>8</v>
       </c>
-      <c r="D33" s="72" t="s">
+      <c r="D33" s="41" t="s">
         <v>1653</v>
       </c>
-      <c r="E33" s="72" t="s">
+      <c r="E33" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="F33" s="72" t="s">
+      <c r="F33" s="41" t="s">
         <v>1654</v>
       </c>
-      <c r="G33" s="72" t="s">
+      <c r="G33" s="41" t="s">
         <v>1655</v>
       </c>
-      <c r="H33" s="72" t="s">
+      <c r="H33" s="41" t="s">
         <v>1637</v>
       </c>
-      <c r="I33" s="72" t="s">
+      <c r="I33" s="41" t="s">
         <v>1656</v>
       </c>
-      <c r="J33" s="72" t="s">
+      <c r="J33" s="41" t="s">
         <v>1657</v>
       </c>
-      <c r="K33" s="72" t="s">
+      <c r="K33" s="41" t="s">
         <v>1658</v>
       </c>
-      <c r="L33" s="72" t="s">
+      <c r="L33" s="41" t="s">
         <v>1659</v>
       </c>
-      <c r="M33" s="72" t="s">
+      <c r="M33" s="41" t="s">
         <v>1608</v>
       </c>
-      <c r="N33" s="72" t="str">
+      <c r="N33" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -18984,7 +18991,7 @@
       <c r="Q33" s="41"/>
       <c r="R33" s="41"/>
       <c r="S33" s="21"/>
-      <c r="V33" s="63"/>
+      <c r="V33" s="65"/>
     </row>
     <row r="34" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="22"/>
@@ -19020,7 +19027,7 @@
       <c r="Q34" s="24"/>
       <c r="R34" s="24"/>
       <c r="S34" s="31"/>
-      <c r="V34" s="63"/>
+      <c r="V34" s="65"/>
     </row>
     <row r="35" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B35" s="12"/>
@@ -19040,7 +19047,7 @@
       <c r="P35" s="60"/>
       <c r="Q35" s="60"/>
       <c r="R35" s="60"/>
-      <c r="V35" s="63"/>
+      <c r="V35" s="65"/>
     </row>
     <row r="36" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="17"/>
@@ -19060,14 +19067,14 @@
       <c r="Q36" s="61"/>
       <c r="R36" s="61"/>
       <c r="S36" s="19"/>
-      <c r="V36" s="63"/>
+      <c r="V36" s="65"/>
     </row>
     <row r="37" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B37" s="20">
         <f>B33+1</f>
         <v>9</v>
       </c>
-      <c r="D37" s="72" t="str">
+      <c r="D37" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -19087,7 +19094,7 @@
       <c r="Q37" s="41"/>
       <c r="R37" s="41"/>
       <c r="S37" s="21"/>
-      <c r="V37" s="63"/>
+      <c r="V37" s="65"/>
     </row>
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="22"/>
@@ -19107,7 +19114,7 @@
       <c r="Q38" s="24"/>
       <c r="R38" s="24"/>
       <c r="S38" s="31"/>
-      <c r="V38" s="63"/>
+      <c r="V38" s="65"/>
     </row>
     <row r="39" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B39" s="12"/>
@@ -19133,7 +19140,7 @@
       <c r="P39" s="54"/>
       <c r="Q39" s="54"/>
       <c r="R39" s="54"/>
-      <c r="V39" s="63"/>
+      <c r="V39" s="65"/>
     </row>
     <row r="40" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="17"/>
@@ -19177,60 +19184,60 @@
         <v>1833</v>
       </c>
       <c r="S40" s="19"/>
-      <c r="V40" s="63"/>
+      <c r="V40" s="65"/>
     </row>
     <row r="41" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B41" s="20">
         <f>B37+1</f>
         <v>10</v>
       </c>
-      <c r="D41" s="72" t="s">
+      <c r="D41" s="41" t="s">
         <v>1660</v>
       </c>
-      <c r="E41" s="72" t="s">
+      <c r="E41" s="41" t="s">
         <v>1661</v>
       </c>
-      <c r="F41" s="72" t="s">
+      <c r="F41" s="41" t="s">
         <v>1607</v>
       </c>
-      <c r="G41" s="72" t="s">
+      <c r="G41" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="H41" s="72" t="s">
+      <c r="H41" s="41" t="s">
         <v>1662</v>
       </c>
-      <c r="I41" s="72" t="s">
+      <c r="I41" s="41" t="s">
         <v>1663</v>
       </c>
-      <c r="J41" s="72" t="s">
+      <c r="J41" s="41" t="s">
         <v>1664</v>
       </c>
-      <c r="K41" s="72" t="s">
+      <c r="K41" s="41" t="s">
         <v>1628</v>
       </c>
-      <c r="L41" s="72" t="s">
+      <c r="L41" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="M41" s="72" t="s">
+      <c r="M41" s="41" t="s">
         <v>1665</v>
       </c>
-      <c r="N41" s="72" t="s">
+      <c r="N41" s="41" t="s">
         <v>1666</v>
       </c>
-      <c r="O41" s="72" t="s">
+      <c r="O41" s="41" t="s">
         <v>1585</v>
       </c>
-      <c r="P41" s="72" t="s">
+      <c r="P41" s="41" t="s">
         <v>1656</v>
       </c>
-      <c r="Q41" s="72" t="s">
+      <c r="Q41" s="41" t="s">
         <v>1608</v>
       </c>
-      <c r="R41" s="72" t="s">
+      <c r="R41" s="41" t="s">
         <v>1667</v>
       </c>
       <c r="S41" s="21"/>
-      <c r="V41" s="63"/>
+      <c r="V41" s="65"/>
     </row>
     <row r="42" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="22"/>
@@ -19274,7 +19281,7 @@
         <v>1976</v>
       </c>
       <c r="S42" s="31"/>
-      <c r="V42" s="63"/>
+      <c r="V42" s="65"/>
     </row>
     <row r="43" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B43" s="12"/>
@@ -19296,7 +19303,7 @@
       <c r="P43" s="54"/>
       <c r="Q43" s="54"/>
       <c r="R43" s="54"/>
-      <c r="V43" s="63"/>
+      <c r="V43" s="65"/>
     </row>
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="17"/>
@@ -19342,60 +19349,60 @@
         <v>597</v>
       </c>
       <c r="S44" s="19"/>
-      <c r="V44" s="63"/>
+      <c r="V44" s="65"/>
     </row>
     <row r="45" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B45" s="20">
         <f>B41+1</f>
         <v>11</v>
       </c>
-      <c r="D45" s="72" t="s">
+      <c r="D45" s="41" t="s">
         <v>1668</v>
       </c>
-      <c r="E45" s="72" t="s">
+      <c r="E45" s="41" t="s">
         <v>1669</v>
       </c>
-      <c r="F45" s="72" t="s">
+      <c r="F45" s="41" t="s">
         <v>1670</v>
       </c>
-      <c r="G45" s="72" t="s">
+      <c r="G45" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="H45" s="72" t="s">
+      <c r="H45" s="41" t="s">
         <v>1671</v>
       </c>
-      <c r="I45" s="72" t="s">
+      <c r="I45" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="J45" s="72" t="s">
+      <c r="J45" s="41" t="s">
         <v>1672</v>
       </c>
-      <c r="K45" s="72" t="s">
+      <c r="K45" s="41" t="s">
         <v>1673</v>
       </c>
-      <c r="L45" s="72" t="s">
+      <c r="L45" s="41" t="s">
         <v>1674</v>
       </c>
-      <c r="M45" s="72" t="s">
+      <c r="M45" s="41" t="s">
         <v>1675</v>
       </c>
-      <c r="N45" s="72" t="s">
+      <c r="N45" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="O45" s="72" t="s">
+      <c r="O45" s="41" t="s">
         <v>1651</v>
       </c>
-      <c r="P45" s="72" t="s">
+      <c r="P45" s="41" t="s">
         <v>1608</v>
       </c>
-      <c r="Q45" s="72" t="s">
+      <c r="Q45" s="41" t="s">
         <v>1676</v>
       </c>
-      <c r="R45" s="72" t="s">
+      <c r="R45" s="41" t="s">
         <v>1637</v>
       </c>
       <c r="S45" s="21"/>
-      <c r="V45" s="63"/>
+      <c r="V45" s="65"/>
     </row>
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="22"/>
@@ -19441,7 +19448,7 @@
         <v>1949</v>
       </c>
       <c r="S46" s="31"/>
-      <c r="V46" s="63"/>
+      <c r="V46" s="65"/>
     </row>
     <row r="47" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B47" s="12"/>
@@ -19463,7 +19470,7 @@
       <c r="P47" s="54"/>
       <c r="Q47" s="54"/>
       <c r="R47" s="54"/>
-      <c r="V47" s="63"/>
+      <c r="V47" s="65"/>
     </row>
     <row r="48" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="17"/>
@@ -19509,60 +19516,60 @@
         <v>1842</v>
       </c>
       <c r="S48" s="19"/>
-      <c r="V48" s="63"/>
+      <c r="V48" s="65"/>
     </row>
     <row r="49" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B49" s="20">
         <f>B45+1</f>
         <v>12</v>
       </c>
-      <c r="D49" s="72" t="s">
+      <c r="D49" s="41" t="s">
         <v>1677</v>
       </c>
-      <c r="E49" s="72" t="s">
+      <c r="E49" s="41" t="s">
         <v>1678</v>
       </c>
-      <c r="F49" s="72" t="s">
+      <c r="F49" s="41" t="s">
         <v>1679</v>
       </c>
-      <c r="G49" s="72" t="s">
+      <c r="G49" s="41" t="s">
         <v>1680</v>
       </c>
-      <c r="H49" s="72" t="s">
+      <c r="H49" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="I49" s="72" t="s">
+      <c r="I49" s="41" t="s">
         <v>1655</v>
       </c>
-      <c r="J49" s="72" t="s">
+      <c r="J49" s="41" t="s">
         <v>1637</v>
       </c>
-      <c r="K49" s="72" t="s">
+      <c r="K49" s="41" t="s">
         <v>1681</v>
       </c>
-      <c r="L49" s="72" t="s">
+      <c r="L49" s="41" t="s">
         <v>1682</v>
       </c>
-      <c r="M49" s="72" t="s">
+      <c r="M49" s="41" t="s">
         <v>1683</v>
       </c>
-      <c r="N49" s="72" t="s">
+      <c r="N49" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="O49" s="72" t="s">
+      <c r="O49" s="41" t="s">
         <v>1684</v>
       </c>
-      <c r="P49" s="72" t="s">
+      <c r="P49" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="Q49" s="72" t="s">
+      <c r="Q49" s="41" t="s">
         <v>1685</v>
       </c>
-      <c r="R49" s="72" t="s">
+      <c r="R49" s="41" t="s">
         <v>1686</v>
       </c>
       <c r="S49" s="21"/>
-      <c r="V49" s="63"/>
+      <c r="V49" s="65"/>
     </row>
     <row r="50" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="22"/>
@@ -19608,7 +19615,7 @@
         <v>1993</v>
       </c>
       <c r="S50" s="31"/>
-      <c r="V50" s="63"/>
+      <c r="V50" s="65"/>
     </row>
     <row r="51" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B51" s="12"/>
@@ -19630,7 +19637,7 @@
       <c r="P51" s="60"/>
       <c r="Q51" s="60"/>
       <c r="R51" s="60"/>
-      <c r="V51" s="63"/>
+      <c r="V51" s="65"/>
     </row>
     <row r="52" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="17"/>
@@ -19654,23 +19661,23 @@
       <c r="Q52" s="61"/>
       <c r="R52" s="61"/>
       <c r="S52" s="19"/>
-      <c r="V52" s="63"/>
+      <c r="V52" s="65"/>
     </row>
     <row r="53" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B53" s="20">
         <f>B49+1</f>
         <v>13</v>
       </c>
-      <c r="D53" s="72" t="s">
+      <c r="D53" s="41" t="s">
         <v>1687</v>
       </c>
-      <c r="E53" s="72" t="s">
+      <c r="E53" s="41" t="s">
         <v>1607</v>
       </c>
-      <c r="F53" s="72" t="s">
+      <c r="F53" s="41" t="s">
         <v>1608</v>
       </c>
-      <c r="G53" s="72" t="str">
+      <c r="G53" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -19687,7 +19694,7 @@
       <c r="Q53" s="41"/>
       <c r="R53" s="41"/>
       <c r="S53" s="21"/>
-      <c r="V53" s="63"/>
+      <c r="V53" s="65"/>
     </row>
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="22"/>
@@ -19711,7 +19718,7 @@
       <c r="Q54" s="24"/>
       <c r="R54" s="24"/>
       <c r="S54" s="31"/>
-      <c r="V54" s="63"/>
+      <c r="V54" s="65"/>
     </row>
     <row r="55" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B55" s="12"/>
@@ -19731,7 +19738,7 @@
       <c r="P55" s="60"/>
       <c r="Q55" s="60"/>
       <c r="R55" s="60"/>
-      <c r="V55" s="63"/>
+      <c r="V55" s="65"/>
     </row>
     <row r="56" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="17"/>
@@ -19751,14 +19758,14 @@
       <c r="Q56" s="61"/>
       <c r="R56" s="61"/>
       <c r="S56" s="19"/>
-      <c r="V56" s="63"/>
+      <c r="V56" s="65"/>
     </row>
     <row r="57" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B57" s="20">
         <f>B53+1</f>
         <v>14</v>
       </c>
-      <c r="D57" s="72" t="str">
+      <c r="D57" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -19778,7 +19785,7 @@
       <c r="Q57" s="41"/>
       <c r="R57" s="41"/>
       <c r="S57" s="21"/>
-      <c r="V57" s="63"/>
+      <c r="V57" s="65"/>
     </row>
     <row r="58" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="22"/>
@@ -19798,7 +19805,7 @@
       <c r="Q58" s="24"/>
       <c r="R58" s="24"/>
       <c r="S58" s="31"/>
-      <c r="V58" s="63"/>
+      <c r="V58" s="65"/>
     </row>
     <row r="59" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B59" s="12"/>
@@ -19830,7 +19837,7 @@
       <c r="P59" s="54"/>
       <c r="Q59" s="54"/>
       <c r="R59" s="54"/>
-      <c r="V59" s="63"/>
+      <c r="V59" s="65"/>
     </row>
     <row r="60" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="17"/>
@@ -19876,60 +19883,60 @@
         <v>762</v>
       </c>
       <c r="S60" s="19"/>
-      <c r="V60" s="63"/>
+      <c r="V60" s="65"/>
     </row>
     <row r="61" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B61" s="20">
         <f>B57+1</f>
         <v>15</v>
       </c>
-      <c r="D61" s="72" t="s">
+      <c r="D61" s="41" t="s">
         <v>1688</v>
       </c>
-      <c r="E61" s="72" t="s">
+      <c r="E61" s="41" t="s">
         <v>1689</v>
       </c>
-      <c r="F61" s="72" t="s">
+      <c r="F61" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="G61" s="72" t="s">
+      <c r="G61" s="41" t="s">
         <v>1690</v>
       </c>
-      <c r="H61" s="72" t="s">
+      <c r="H61" s="41" t="s">
         <v>1691</v>
       </c>
-      <c r="I61" s="72" t="s">
+      <c r="I61" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="J61" s="72" t="s">
+      <c r="J61" s="41" t="s">
         <v>1672</v>
       </c>
-      <c r="K61" s="72" t="s">
+      <c r="K61" s="41" t="s">
         <v>1667</v>
       </c>
-      <c r="L61" s="72" t="s">
+      <c r="L61" s="41" t="s">
         <v>1652</v>
       </c>
-      <c r="M61" s="72" t="s">
+      <c r="M61" s="41" t="s">
         <v>1692</v>
       </c>
-      <c r="N61" s="72" t="s">
+      <c r="N61" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="O61" s="72" t="s">
+      <c r="O61" s="41" t="s">
         <v>1693</v>
       </c>
-      <c r="P61" s="72" t="s">
+      <c r="P61" s="41" t="s">
         <v>1694</v>
       </c>
-      <c r="Q61" s="72" t="s">
+      <c r="Q61" s="41" t="s">
         <v>1695</v>
       </c>
-      <c r="R61" s="72" t="s">
+      <c r="R61" s="41" t="s">
         <v>1680</v>
       </c>
       <c r="S61" s="21"/>
-      <c r="V61" s="63"/>
+      <c r="V61" s="65"/>
     </row>
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="22"/>
@@ -19975,7 +19982,7 @@
         <v>1989</v>
       </c>
       <c r="S62" s="31"/>
-      <c r="V62" s="63"/>
+      <c r="V62" s="65"/>
     </row>
     <row r="63" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B63" s="12"/>
@@ -20007,7 +20014,7 @@
       <c r="P63" s="54"/>
       <c r="Q63" s="54"/>
       <c r="R63" s="54"/>
-      <c r="V63" s="63"/>
+      <c r="V63" s="65"/>
     </row>
     <row r="64" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B64" s="17"/>
@@ -20051,60 +20058,60 @@
       </c>
       <c r="R64" s="18"/>
       <c r="S64" s="19"/>
-      <c r="V64" s="63"/>
+      <c r="V64" s="65"/>
     </row>
     <row r="65" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B65" s="20">
         <f>B61+1</f>
         <v>16</v>
       </c>
-      <c r="D65" s="72" t="s">
+      <c r="D65" s="41" t="s">
         <v>1696</v>
       </c>
-      <c r="E65" s="72" t="s">
+      <c r="E65" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="F65" s="72" t="s">
+      <c r="F65" s="41" t="s">
         <v>1697</v>
       </c>
-      <c r="G65" s="72" t="s">
+      <c r="G65" s="41" t="s">
         <v>1698</v>
       </c>
-      <c r="H65" s="72" t="s">
+      <c r="H65" s="41" t="s">
         <v>1652</v>
       </c>
-      <c r="I65" s="72" t="s">
+      <c r="I65" s="41" t="s">
         <v>1699</v>
       </c>
-      <c r="J65" s="72" t="s">
+      <c r="J65" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="K65" s="72" t="s">
+      <c r="K65" s="41" t="s">
         <v>1700</v>
       </c>
-      <c r="L65" s="72" t="s">
+      <c r="L65" s="41" t="s">
         <v>1626</v>
       </c>
-      <c r="M65" s="72" t="s">
+      <c r="M65" s="41" t="s">
         <v>1693</v>
       </c>
-      <c r="N65" s="72" t="s">
+      <c r="N65" s="41" t="s">
         <v>1701</v>
       </c>
-      <c r="O65" s="72" t="s">
+      <c r="O65" s="41" t="s">
         <v>1702</v>
       </c>
-      <c r="P65" s="72" t="s">
+      <c r="P65" s="41" t="s">
         <v>1676</v>
       </c>
-      <c r="Q65" s="72" t="s">
+      <c r="Q65" s="41" t="s">
         <v>1703</v>
       </c>
-      <c r="R65" s="72" t="s">
+      <c r="R65" s="41" t="s">
         <v>1588</v>
       </c>
       <c r="S65" s="21"/>
-      <c r="V65" s="63"/>
+      <c r="V65" s="65"/>
     </row>
     <row r="66" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="22"/>
@@ -20148,7 +20155,7 @@
       </c>
       <c r="R66" s="24"/>
       <c r="S66" s="31"/>
-      <c r="V66" s="63"/>
+      <c r="V66" s="65"/>
     </row>
     <row r="67" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B67" s="12"/>
@@ -20172,7 +20179,7 @@
       <c r="P67" s="54"/>
       <c r="Q67" s="54"/>
       <c r="R67" s="54"/>
-      <c r="V67" s="63"/>
+      <c r="V67" s="65"/>
     </row>
     <row r="68" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="17"/>
@@ -20218,60 +20225,60 @@
         <v>1858</v>
       </c>
       <c r="S68" s="19"/>
-      <c r="V68" s="63"/>
+      <c r="V68" s="65"/>
     </row>
     <row r="69" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B69" s="20">
         <f>B65+1</f>
         <v>17</v>
       </c>
-      <c r="D69" s="72" t="s">
+      <c r="D69" s="41" t="s">
         <v>1704</v>
       </c>
-      <c r="E69" s="72" t="s">
+      <c r="E69" s="41" t="s">
         <v>1705</v>
       </c>
-      <c r="F69" s="72" t="s">
+      <c r="F69" s="41" t="s">
         <v>1706</v>
       </c>
-      <c r="G69" s="72" t="s">
+      <c r="G69" s="41" t="s">
         <v>1707</v>
       </c>
-      <c r="H69" s="72" t="s">
+      <c r="H69" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="I69" s="72" t="s">
+      <c r="I69" s="41" t="s">
         <v>1708</v>
       </c>
-      <c r="J69" s="72" t="s">
+      <c r="J69" s="41" t="s">
         <v>1608</v>
       </c>
-      <c r="K69" s="72" t="s">
+      <c r="K69" s="41" t="s">
         <v>1646</v>
       </c>
-      <c r="L69" s="72" t="s">
+      <c r="L69" s="41" t="s">
         <v>1694</v>
       </c>
-      <c r="M69" s="72" t="s">
+      <c r="M69" s="41" t="s">
         <v>1709</v>
       </c>
-      <c r="N69" s="72" t="s">
+      <c r="N69" s="41" t="s">
         <v>1710</v>
       </c>
-      <c r="O69" s="72" t="s">
+      <c r="O69" s="41" t="s">
         <v>1711</v>
       </c>
-      <c r="P69" s="72" t="s">
+      <c r="P69" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="Q69" s="72" t="s">
+      <c r="Q69" s="41" t="s">
         <v>1712</v>
       </c>
-      <c r="R69" s="72" t="s">
+      <c r="R69" s="41" t="s">
         <v>1713</v>
       </c>
       <c r="S69" s="21"/>
-      <c r="V69" s="63"/>
+      <c r="V69" s="65"/>
     </row>
     <row r="70" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="22"/>
@@ -20317,7 +20324,7 @@
         <v>2021</v>
       </c>
       <c r="S70" s="31"/>
-      <c r="V70" s="63"/>
+      <c r="V70" s="65"/>
     </row>
     <row r="71" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B71" s="12"/>
@@ -20349,7 +20356,7 @@
         <v>884</v>
       </c>
       <c r="R71" s="54"/>
-      <c r="V71" s="63"/>
+      <c r="V71" s="65"/>
     </row>
     <row r="72" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="17"/>
@@ -20393,60 +20400,60 @@
       </c>
       <c r="R72" s="18"/>
       <c r="S72" s="19"/>
-      <c r="V72" s="63"/>
+      <c r="V72" s="65"/>
     </row>
     <row r="73" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B73" s="20">
         <f>B69+1</f>
         <v>18</v>
       </c>
-      <c r="D73" s="72" t="s">
+      <c r="D73" s="41" t="s">
         <v>1714</v>
       </c>
-      <c r="E73" s="72" t="s">
+      <c r="E73" s="41" t="s">
         <v>1715</v>
       </c>
-      <c r="F73" s="72" t="s">
+      <c r="F73" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="G73" s="72" t="s">
+      <c r="G73" s="41" t="s">
         <v>1716</v>
       </c>
-      <c r="H73" s="72" t="s">
+      <c r="H73" s="41" t="s">
         <v>1644</v>
       </c>
-      <c r="I73" s="72" t="s">
+      <c r="I73" s="41" t="s">
         <v>1717</v>
       </c>
-      <c r="J73" s="72" t="s">
+      <c r="J73" s="41" t="s">
         <v>1598</v>
       </c>
-      <c r="K73" s="72" t="s">
+      <c r="K73" s="41" t="s">
         <v>1676</v>
       </c>
-      <c r="L73" s="72" t="s">
+      <c r="L73" s="41" t="s">
         <v>1718</v>
       </c>
-      <c r="M73" s="72" t="s">
+      <c r="M73" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="N73" s="72" t="s">
+      <c r="N73" s="41" t="s">
         <v>1719</v>
       </c>
-      <c r="O73" s="72" t="s">
+      <c r="O73" s="41" t="s">
         <v>1720</v>
       </c>
-      <c r="P73" s="72" t="s">
+      <c r="P73" s="41" t="s">
         <v>1598</v>
       </c>
-      <c r="Q73" s="72" t="s">
+      <c r="Q73" s="41" t="s">
         <v>1721</v>
       </c>
-      <c r="R73" s="72" t="s">
+      <c r="R73" s="41" t="s">
         <v>1588</v>
       </c>
       <c r="S73" s="21"/>
-      <c r="V73" s="63"/>
+      <c r="V73" s="65"/>
     </row>
     <row r="74" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="22"/>
@@ -20490,7 +20497,7 @@
       </c>
       <c r="R74" s="24"/>
       <c r="S74" s="31"/>
-      <c r="V74" s="63"/>
+      <c r="V74" s="65"/>
     </row>
     <row r="75" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B75" s="12"/>
@@ -20520,7 +20527,7 @@
       <c r="P75" s="54"/>
       <c r="Q75" s="54"/>
       <c r="R75" s="54"/>
-      <c r="V75" s="63"/>
+      <c r="V75" s="65"/>
     </row>
     <row r="76" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="17"/>
@@ -20566,60 +20573,60 @@
         <v>1839</v>
       </c>
       <c r="S76" s="19"/>
-      <c r="V76" s="63"/>
+      <c r="V76" s="65"/>
     </row>
     <row r="77" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B77" s="20">
         <f>B73+1</f>
         <v>19</v>
       </c>
-      <c r="D77" s="72" t="s">
+      <c r="D77" s="41" t="s">
         <v>1722</v>
       </c>
-      <c r="E77" s="72" t="s">
+      <c r="E77" s="41" t="s">
         <v>1723</v>
       </c>
-      <c r="F77" s="72" t="s">
+      <c r="F77" s="41" t="s">
         <v>1724</v>
       </c>
-      <c r="G77" s="72" t="s">
+      <c r="G77" s="41" t="s">
         <v>1655</v>
       </c>
-      <c r="H77" s="72" t="s">
+      <c r="H77" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="I77" s="72" t="s">
+      <c r="I77" s="41" t="s">
         <v>1714</v>
       </c>
-      <c r="J77" s="72" t="s">
+      <c r="J77" s="41" t="s">
         <v>1725</v>
       </c>
-      <c r="K77" s="72" t="s">
+      <c r="K77" s="41" t="s">
         <v>1726</v>
       </c>
-      <c r="L77" s="72" t="s">
+      <c r="L77" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="M77" s="72" t="s">
+      <c r="M77" s="41" t="s">
         <v>1727</v>
       </c>
-      <c r="N77" s="72" t="s">
+      <c r="N77" s="41" t="s">
         <v>1612</v>
       </c>
-      <c r="O77" s="72" t="s">
+      <c r="O77" s="41" t="s">
         <v>1626</v>
       </c>
-      <c r="P77" s="72" t="s">
+      <c r="P77" s="41" t="s">
         <v>1728</v>
       </c>
-      <c r="Q77" s="72" t="s">
+      <c r="Q77" s="41" t="s">
         <v>1644</v>
       </c>
-      <c r="R77" s="72" t="s">
+      <c r="R77" s="41" t="s">
         <v>1676</v>
       </c>
       <c r="S77" s="21"/>
-      <c r="V77" s="63"/>
+      <c r="V77" s="65"/>
     </row>
     <row r="78" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="22"/>
@@ -20665,7 +20672,7 @@
         <v>1985</v>
       </c>
       <c r="S78" s="31"/>
-      <c r="V78" s="63"/>
+      <c r="V78" s="65"/>
     </row>
     <row r="79" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B79" s="12"/>
@@ -20687,7 +20694,7 @@
       <c r="P79" s="54"/>
       <c r="Q79" s="54"/>
       <c r="R79" s="54"/>
-      <c r="V79" s="63"/>
+      <c r="V79" s="65"/>
     </row>
     <row r="80" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="17"/>
@@ -20731,60 +20738,60 @@
       </c>
       <c r="R80" s="18"/>
       <c r="S80" s="19"/>
-      <c r="V80" s="63"/>
+      <c r="V80" s="65"/>
     </row>
     <row r="81" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B81" s="20">
         <f>B77+1</f>
         <v>20</v>
       </c>
-      <c r="D81" s="72" t="s">
+      <c r="D81" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="E81" s="72" t="s">
+      <c r="E81" s="41" t="s">
         <v>1729</v>
       </c>
-      <c r="F81" s="72" t="s">
+      <c r="F81" s="41" t="s">
         <v>1730</v>
       </c>
-      <c r="G81" s="72" t="s">
+      <c r="G81" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="H81" s="72" t="s">
+      <c r="H81" s="41" t="s">
         <v>1659</v>
       </c>
-      <c r="I81" s="72" t="s">
+      <c r="I81" s="41" t="s">
         <v>1731</v>
       </c>
-      <c r="J81" s="72" t="s">
+      <c r="J81" s="41" t="s">
         <v>1606</v>
       </c>
-      <c r="K81" s="72" t="s">
+      <c r="K81" s="41" t="s">
         <v>1732</v>
       </c>
-      <c r="L81" s="72" t="s">
+      <c r="L81" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="M81" s="72" t="s">
+      <c r="M81" s="41" t="s">
         <v>1733</v>
       </c>
-      <c r="N81" s="72" t="s">
+      <c r="N81" s="41" t="s">
         <v>1734</v>
       </c>
-      <c r="O81" s="72" t="s">
+      <c r="O81" s="41" t="s">
         <v>1735</v>
       </c>
-      <c r="P81" s="72" t="s">
+      <c r="P81" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="Q81" s="72" t="s">
+      <c r="Q81" s="41" t="s">
         <v>1736</v>
       </c>
-      <c r="R81" s="72" t="s">
+      <c r="R81" s="41" t="s">
         <v>1608</v>
       </c>
       <c r="S81" s="21"/>
-      <c r="V81" s="63"/>
+      <c r="V81" s="65"/>
     </row>
     <row r="82" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="22"/>
@@ -20828,7 +20835,7 @@
       </c>
       <c r="R82" s="24"/>
       <c r="S82" s="31"/>
-      <c r="V82" s="64"/>
+      <c r="V82" s="66"/>
     </row>
     <row r="83" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B83" s="12"/>
@@ -20907,49 +20914,49 @@
         <f>B81+1</f>
         <v>21</v>
       </c>
-      <c r="D85" s="72" t="s">
+      <c r="D85" s="41" t="s">
         <v>1737</v>
       </c>
-      <c r="E85" s="72" t="s">
+      <c r="E85" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="F85" s="72" t="s">
+      <c r="F85" s="41" t="s">
         <v>1676</v>
       </c>
-      <c r="G85" s="72" t="s">
+      <c r="G85" s="41" t="s">
         <v>1717</v>
       </c>
-      <c r="H85" s="72" t="s">
+      <c r="H85" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="I85" s="72" t="s">
+      <c r="I85" s="41" t="s">
         <v>1672</v>
       </c>
-      <c r="J85" s="72" t="s">
+      <c r="J85" s="41" t="s">
         <v>1667</v>
       </c>
-      <c r="K85" s="72" t="s">
+      <c r="K85" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="L85" s="72" t="s">
+      <c r="L85" s="41" t="s">
         <v>1738</v>
       </c>
-      <c r="M85" s="72" t="s">
+      <c r="M85" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="N85" s="72" t="s">
+      <c r="N85" s="41" t="s">
         <v>1739</v>
       </c>
-      <c r="O85" s="72" t="s">
+      <c r="O85" s="41" t="s">
         <v>1638</v>
       </c>
-      <c r="P85" s="72" t="s">
+      <c r="P85" s="41" t="s">
         <v>1740</v>
       </c>
-      <c r="Q85" s="72" t="s">
+      <c r="Q85" s="41" t="s">
         <v>1741</v>
       </c>
-      <c r="R85" s="72" t="s">
+      <c r="R85" s="41" t="s">
         <v>1588</v>
       </c>
       <c r="S85" s="21"/>
@@ -21076,49 +21083,49 @@
         <f>B85+1</f>
         <v>22</v>
       </c>
-      <c r="D89" s="72" t="s">
+      <c r="D89" s="41" t="s">
         <v>1742</v>
       </c>
-      <c r="E89" s="72" t="s">
+      <c r="E89" s="41" t="s">
         <v>1714</v>
       </c>
-      <c r="F89" s="72" t="s">
+      <c r="F89" s="41" t="s">
         <v>1743</v>
       </c>
-      <c r="G89" s="72" t="s">
+      <c r="G89" s="41" t="s">
         <v>1714</v>
       </c>
-      <c r="H89" s="72" t="s">
+      <c r="H89" s="41" t="s">
         <v>1637</v>
       </c>
-      <c r="I89" s="72" t="s">
+      <c r="I89" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="J89" s="72" t="s">
+      <c r="J89" s="41" t="s">
         <v>1744</v>
       </c>
-      <c r="K89" s="72" t="s">
+      <c r="K89" s="41" t="s">
         <v>1680</v>
       </c>
-      <c r="L89" s="72" t="s">
+      <c r="L89" s="41" t="s">
         <v>1626</v>
       </c>
-      <c r="M89" s="72" t="s">
+      <c r="M89" s="41" t="s">
         <v>1745</v>
       </c>
-      <c r="N89" s="72" t="s">
+      <c r="N89" s="41" t="s">
         <v>1746</v>
       </c>
-      <c r="O89" s="72" t="s">
+      <c r="O89" s="41" t="s">
         <v>1747</v>
       </c>
-      <c r="P89" s="72" t="s">
+      <c r="P89" s="41" t="s">
         <v>1731</v>
       </c>
-      <c r="Q89" s="72" t="s">
+      <c r="Q89" s="41" t="s">
         <v>1748</v>
       </c>
-      <c r="R89" s="72" t="s">
+      <c r="R89" s="41" t="s">
         <v>1588</v>
       </c>
       <c r="S89" s="21"/>
@@ -21249,49 +21256,49 @@
         <f>B89+1</f>
         <v>23</v>
       </c>
-      <c r="D93" s="72" t="s">
+      <c r="D93" s="41" t="s">
         <v>1749</v>
       </c>
-      <c r="E93" s="72" t="s">
+      <c r="E93" s="41" t="s">
         <v>1750</v>
       </c>
-      <c r="F93" s="72" t="s">
+      <c r="F93" s="41" t="s">
         <v>1598</v>
       </c>
-      <c r="G93" s="72" t="s">
+      <c r="G93" s="41" t="s">
         <v>1751</v>
       </c>
-      <c r="H93" s="72" t="s">
+      <c r="H93" s="41" t="s">
         <v>1608</v>
       </c>
-      <c r="I93" s="72" t="s">
+      <c r="I93" s="41" t="s">
         <v>1752</v>
       </c>
-      <c r="J93" s="72" t="s">
+      <c r="J93" s="41" t="s">
         <v>1689</v>
       </c>
-      <c r="K93" s="72" t="s">
+      <c r="K93" s="41" t="s">
         <v>1753</v>
       </c>
-      <c r="L93" s="72" t="s">
+      <c r="L93" s="41" t="s">
         <v>1754</v>
       </c>
-      <c r="M93" s="72" t="s">
+      <c r="M93" s="41" t="s">
         <v>1755</v>
       </c>
-      <c r="N93" s="72" t="s">
+      <c r="N93" s="41" t="s">
         <v>1756</v>
       </c>
-      <c r="O93" s="72" t="s">
+      <c r="O93" s="41" t="s">
         <v>1757</v>
       </c>
-      <c r="P93" s="72" t="s">
+      <c r="P93" s="41" t="s">
         <v>1654</v>
       </c>
-      <c r="Q93" s="72" t="s">
+      <c r="Q93" s="41" t="s">
         <v>1671</v>
       </c>
-      <c r="R93" s="72" t="s">
+      <c r="R93" s="41" t="s">
         <v>1736</v>
       </c>
       <c r="S93" s="21"/>
@@ -21398,28 +21405,28 @@
         <f>B93+1</f>
         <v>24</v>
       </c>
-      <c r="D97" s="72" t="s">
+      <c r="D97" s="41" t="s">
         <v>1608</v>
       </c>
-      <c r="E97" s="72" t="s">
+      <c r="E97" s="41" t="s">
         <v>1758</v>
       </c>
-      <c r="F97" s="72" t="s">
+      <c r="F97" s="41" t="s">
         <v>1759</v>
       </c>
-      <c r="G97" s="72" t="s">
+      <c r="G97" s="41" t="s">
         <v>1714</v>
       </c>
-      <c r="H97" s="72" t="s">
+      <c r="H97" s="41" t="s">
         <v>1760</v>
       </c>
-      <c r="I97" s="72" t="s">
+      <c r="I97" s="41" t="s">
         <v>1761</v>
       </c>
-      <c r="J97" s="72" t="s">
+      <c r="J97" s="41" t="s">
         <v>1762</v>
       </c>
-      <c r="K97" s="72" t="str">
+      <c r="K97" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -21507,7 +21514,7 @@
         <f>B97+1</f>
         <v>25</v>
       </c>
-      <c r="D101" s="72" t="str">
+      <c r="D101" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -21626,49 +21633,49 @@
         <f>B101+1</f>
         <v>26</v>
       </c>
-      <c r="D105" s="72" t="s">
+      <c r="D105" s="41" t="s">
         <v>1763</v>
       </c>
-      <c r="E105" s="72" t="s">
+      <c r="E105" s="41" t="s">
         <v>1764</v>
       </c>
-      <c r="F105" s="72" t="s">
+      <c r="F105" s="41" t="s">
         <v>1765</v>
       </c>
-      <c r="G105" s="72" t="s">
+      <c r="G105" s="41" t="s">
         <v>1689</v>
       </c>
-      <c r="H105" s="72" t="s">
+      <c r="H105" s="41" t="s">
         <v>1744</v>
       </c>
-      <c r="I105" s="72" t="s">
+      <c r="I105" s="41" t="s">
         <v>1733</v>
       </c>
-      <c r="J105" s="72" t="s">
+      <c r="J105" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="K105" s="72" t="s">
+      <c r="K105" s="41" t="s">
         <v>1766</v>
       </c>
-      <c r="L105" s="72" t="s">
+      <c r="L105" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="M105" s="72" t="s">
+      <c r="M105" s="41" t="s">
         <v>1767</v>
       </c>
-      <c r="N105" s="72" t="s">
+      <c r="N105" s="41" t="s">
         <v>1768</v>
       </c>
-      <c r="O105" s="72" t="s">
+      <c r="O105" s="41" t="s">
         <v>1652</v>
       </c>
-      <c r="P105" s="72" t="s">
+      <c r="P105" s="41" t="s">
         <v>1769</v>
       </c>
-      <c r="Q105" s="72" t="s">
+      <c r="Q105" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="R105" s="72" t="s">
+      <c r="R105" s="41" t="s">
         <v>1770</v>
       </c>
       <c r="S105" s="21"/>
@@ -21795,49 +21802,49 @@
         <f>B105+1</f>
         <v>27</v>
       </c>
-      <c r="D109" s="72" t="s">
+      <c r="D109" s="41" t="s">
         <v>1771</v>
       </c>
-      <c r="E109" s="72" t="s">
+      <c r="E109" s="41" t="s">
         <v>1714</v>
       </c>
-      <c r="F109" s="72" t="s">
+      <c r="F109" s="41" t="s">
         <v>1772</v>
       </c>
-      <c r="G109" s="72" t="s">
+      <c r="G109" s="41" t="s">
         <v>1773</v>
       </c>
-      <c r="H109" s="72" t="s">
+      <c r="H109" s="41" t="s">
         <v>1774</v>
       </c>
-      <c r="I109" s="72" t="s">
+      <c r="I109" s="41" t="s">
         <v>1775</v>
       </c>
-      <c r="J109" s="72" t="s">
+      <c r="J109" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="K109" s="72" t="s">
+      <c r="K109" s="41" t="s">
         <v>1714</v>
       </c>
-      <c r="L109" s="72" t="s">
+      <c r="L109" s="41" t="s">
         <v>1743</v>
       </c>
-      <c r="M109" s="72" t="s">
+      <c r="M109" s="41" t="s">
         <v>1776</v>
       </c>
-      <c r="N109" s="72" t="s">
+      <c r="N109" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="O109" s="72" t="s">
+      <c r="O109" s="41" t="s">
         <v>1598</v>
       </c>
-      <c r="P109" s="72" t="s">
+      <c r="P109" s="41" t="s">
         <v>1680</v>
       </c>
-      <c r="Q109" s="72" t="s">
+      <c r="Q109" s="41" t="s">
         <v>1608</v>
       </c>
-      <c r="R109" s="72" t="s">
+      <c r="R109" s="41" t="s">
         <v>1777</v>
       </c>
       <c r="S109" s="21"/>
@@ -21972,49 +21979,49 @@
         <f>B109+1</f>
         <v>28</v>
       </c>
-      <c r="D113" s="72" t="s">
+      <c r="D113" s="41" t="s">
         <v>1725</v>
       </c>
-      <c r="E113" s="72" t="s">
+      <c r="E113" s="41" t="s">
         <v>1652</v>
       </c>
-      <c r="F113" s="72" t="s">
+      <c r="F113" s="41" t="s">
         <v>1756</v>
       </c>
-      <c r="G113" s="72" t="s">
+      <c r="G113" s="41" t="s">
         <v>1757</v>
       </c>
-      <c r="H113" s="72" t="s">
+      <c r="H113" s="41" t="s">
         <v>1638</v>
       </c>
-      <c r="I113" s="72" t="s">
+      <c r="I113" s="41" t="s">
         <v>1778</v>
       </c>
-      <c r="J113" s="72" t="s">
+      <c r="J113" s="41" t="s">
         <v>1779</v>
       </c>
-      <c r="K113" s="72" t="s">
+      <c r="K113" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="L113" s="72" t="s">
+      <c r="L113" s="41" t="s">
         <v>1780</v>
       </c>
-      <c r="M113" s="72" t="s">
+      <c r="M113" s="41" t="s">
         <v>1781</v>
       </c>
-      <c r="N113" s="72" t="s">
+      <c r="N113" s="41" t="s">
         <v>1782</v>
       </c>
-      <c r="O113" s="72" t="s">
+      <c r="O113" s="41" t="s">
         <v>1638</v>
       </c>
-      <c r="P113" s="72" t="s">
+      <c r="P113" s="41" t="s">
         <v>1783</v>
       </c>
-      <c r="Q113" s="72" t="s">
+      <c r="Q113" s="41" t="s">
         <v>1784</v>
       </c>
-      <c r="R113" s="72" t="s">
+      <c r="R113" s="41" t="s">
         <v>1608</v>
       </c>
       <c r="S113" s="21"/>
@@ -22145,49 +22152,49 @@
         <f>B113+1</f>
         <v>29</v>
       </c>
-      <c r="D117" s="67" t="s">
+      <c r="D117" s="44" t="s">
         <v>1785</v>
       </c>
-      <c r="E117" s="67" t="s">
+      <c r="E117" s="44" t="s">
         <v>1595</v>
       </c>
-      <c r="F117" s="67" t="s">
+      <c r="F117" s="44" t="s">
         <v>1682</v>
       </c>
-      <c r="G117" s="67" t="s">
+      <c r="G117" s="44" t="s">
         <v>1786</v>
       </c>
-      <c r="H117" s="67" t="s">
+      <c r="H117" s="44" t="s">
         <v>1588</v>
       </c>
-      <c r="I117" s="67" t="s">
+      <c r="I117" s="44" t="s">
         <v>1654</v>
       </c>
-      <c r="J117" s="67" t="s">
+      <c r="J117" s="44" t="s">
         <v>1742</v>
       </c>
-      <c r="K117" s="67" t="s">
+      <c r="K117" s="44" t="s">
         <v>1786</v>
       </c>
-      <c r="L117" s="67" t="s">
+      <c r="L117" s="44" t="s">
         <v>1595</v>
       </c>
-      <c r="M117" s="67" t="s">
+      <c r="M117" s="44" t="s">
         <v>1682</v>
       </c>
-      <c r="N117" s="67" t="s">
+      <c r="N117" s="44" t="s">
         <v>1765</v>
       </c>
-      <c r="O117" s="67" t="s">
+      <c r="O117" s="44" t="s">
         <v>1588</v>
       </c>
-      <c r="P117" s="67" t="s">
+      <c r="P117" s="44" t="s">
         <v>1787</v>
       </c>
-      <c r="Q117" s="67" t="s">
+      <c r="Q117" s="44" t="s">
         <v>1688</v>
       </c>
-      <c r="R117" s="67" t="s">
+      <c r="R117" s="44" t="s">
         <v>1762</v>
       </c>
       <c r="S117" s="21"/>
@@ -22314,49 +22321,49 @@
         <f>B117+1</f>
         <v>30</v>
       </c>
-      <c r="D121" s="72" t="s">
+      <c r="D121" s="41" t="s">
         <v>1788</v>
       </c>
-      <c r="E121" s="72" t="s">
+      <c r="E121" s="41" t="s">
         <v>1642</v>
       </c>
-      <c r="F121" s="72" t="s">
+      <c r="F121" s="41" t="s">
         <v>1657</v>
       </c>
-      <c r="G121" s="72" t="s">
+      <c r="G121" s="41" t="s">
         <v>1789</v>
       </c>
-      <c r="H121" s="72" t="s">
+      <c r="H121" s="41" t="s">
         <v>1689</v>
       </c>
-      <c r="I121" s="72" t="s">
+      <c r="I121" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="J121" s="72" t="s">
+      <c r="J121" s="41" t="s">
         <v>1790</v>
       </c>
-      <c r="K121" s="72" t="s">
+      <c r="K121" s="41" t="s">
         <v>1644</v>
       </c>
-      <c r="L121" s="72" t="s">
+      <c r="L121" s="41" t="s">
         <v>1676</v>
       </c>
-      <c r="M121" s="72" t="s">
+      <c r="M121" s="41" t="s">
         <v>1791</v>
       </c>
-      <c r="N121" s="72" t="s">
+      <c r="N121" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="O121" s="72" t="s">
+      <c r="O121" s="41" t="s">
         <v>1646</v>
       </c>
-      <c r="P121" s="72" t="s">
+      <c r="P121" s="41" t="s">
         <v>1692</v>
       </c>
-      <c r="Q121" s="72" t="s">
+      <c r="Q121" s="41" t="s">
         <v>1711</v>
       </c>
-      <c r="R121" s="72" t="s">
+      <c r="R121" s="41" t="s">
         <v>1606</v>
       </c>
       <c r="S121" s="21"/>
@@ -22481,49 +22488,49 @@
         <f>B121+1</f>
         <v>31</v>
       </c>
-      <c r="D125" s="72" t="s">
+      <c r="D125" s="41" t="s">
         <v>1792</v>
       </c>
-      <c r="E125" s="72" t="s">
+      <c r="E125" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="F125" s="72" t="s">
+      <c r="F125" s="41" t="s">
         <v>1676</v>
       </c>
-      <c r="G125" s="72" t="s">
+      <c r="G125" s="41" t="s">
         <v>1637</v>
       </c>
-      <c r="H125" s="72" t="s">
+      <c r="H125" s="41" t="s">
         <v>1744</v>
       </c>
-      <c r="I125" s="72" t="s">
+      <c r="I125" s="41" t="s">
         <v>1680</v>
       </c>
-      <c r="J125" s="72" t="s">
+      <c r="J125" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="K125" s="72" t="s">
+      <c r="K125" s="41" t="s">
         <v>1644</v>
       </c>
-      <c r="L125" s="72" t="s">
+      <c r="L125" s="41" t="s">
         <v>1793</v>
       </c>
-      <c r="M125" s="72" t="s">
+      <c r="M125" s="41" t="s">
         <v>1652</v>
       </c>
-      <c r="N125" s="72" t="s">
+      <c r="N125" s="41" t="s">
         <v>1607</v>
       </c>
-      <c r="O125" s="72" t="s">
+      <c r="O125" s="41" t="s">
         <v>1608</v>
       </c>
-      <c r="P125" s="72" t="s">
+      <c r="P125" s="41" t="s">
         <v>1785</v>
       </c>
-      <c r="Q125" s="72" t="s">
+      <c r="Q125" s="41" t="s">
         <v>1595</v>
       </c>
-      <c r="R125" s="72" t="s">
+      <c r="R125" s="41" t="s">
         <v>1764</v>
       </c>
       <c r="S125" s="21"/>
@@ -22642,37 +22649,37 @@
         <f>B125+1</f>
         <v>32</v>
       </c>
-      <c r="D129" s="72" t="s">
+      <c r="D129" s="41" t="s">
         <v>1794</v>
       </c>
-      <c r="E129" s="72" t="s">
+      <c r="E129" s="41" t="s">
         <v>1588</v>
       </c>
-      <c r="F129" s="72" t="s">
+      <c r="F129" s="41" t="s">
         <v>1654</v>
       </c>
-      <c r="G129" s="72" t="s">
+      <c r="G129" s="41" t="s">
         <v>1727</v>
       </c>
-      <c r="H129" s="72" t="s">
+      <c r="H129" s="41" t="s">
         <v>1619</v>
       </c>
-      <c r="I129" s="72" t="s">
+      <c r="I129" s="41" t="s">
         <v>1733</v>
       </c>
-      <c r="J129" s="72" t="s">
+      <c r="J129" s="41" t="s">
         <v>1598</v>
       </c>
-      <c r="K129" s="72" t="s">
+      <c r="K129" s="41" t="s">
         <v>1795</v>
       </c>
-      <c r="L129" s="72" t="s">
+      <c r="L129" s="41" t="s">
         <v>1773</v>
       </c>
-      <c r="M129" s="72" t="s">
+      <c r="M129" s="41" t="s">
         <v>1608</v>
       </c>
-      <c r="N129" s="72" t="s">
+      <c r="N129" s="41" t="s">
         <v>38</v>
       </c>
       <c r="O129" s="41"/>
@@ -29709,292 +29716,292 @@
     <mergeCell ref="V3:V82"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D7:R7">
-    <cfRule type="expression" dxfId="251" priority="97">
+  <conditionalFormatting sqref="D3:R3 D127:R127 D131:R131 D135:R135 D139:R139 D143:R143 D147:R147 D151:R151 D155:R155 D159:R159 D163:R163">
+    <cfRule type="expression" dxfId="251" priority="144">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="250" priority="143">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="250" priority="98">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7:R7">
+    <cfRule type="expression" dxfId="249" priority="98">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="248" priority="97">
+      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:R11">
-    <cfRule type="expression" dxfId="249" priority="57">
+    <cfRule type="expression" dxfId="247" priority="58">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="246" priority="57">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="248" priority="58">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:R15">
-    <cfRule type="expression" dxfId="247" priority="55">
+    <cfRule type="expression" dxfId="245" priority="56">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="244" priority="55">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="246" priority="56">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:R19">
-    <cfRule type="expression" dxfId="245" priority="53">
+    <cfRule type="expression" dxfId="243" priority="54">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="242" priority="53">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="244" priority="54">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23:R23">
-    <cfRule type="expression" dxfId="243" priority="51">
+    <cfRule type="expression" dxfId="241" priority="52">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="240" priority="51">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="242" priority="52">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27:R27">
-    <cfRule type="expression" dxfId="241" priority="49">
+    <cfRule type="expression" dxfId="239" priority="49">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="240" priority="50">
+    <cfRule type="expression" dxfId="238" priority="50">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D31:R31">
-    <cfRule type="expression" dxfId="239" priority="47">
+    <cfRule type="expression" dxfId="237" priority="48">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="236" priority="47">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="238" priority="48">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35:R35">
-    <cfRule type="expression" dxfId="237" priority="45">
+    <cfRule type="expression" dxfId="235" priority="46">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="234" priority="45">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="236" priority="46">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:R39">
-    <cfRule type="expression" dxfId="235" priority="43">
+    <cfRule type="expression" dxfId="233" priority="44">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="232" priority="43">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="234" priority="44">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:R43">
-    <cfRule type="expression" dxfId="233" priority="41">
+    <cfRule type="expression" dxfId="231" priority="42">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="230" priority="41">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="232" priority="42">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:R47">
-    <cfRule type="expression" dxfId="231" priority="39">
+    <cfRule type="expression" dxfId="229" priority="40">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="228" priority="39">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="230" priority="40">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:R51">
-    <cfRule type="expression" dxfId="229" priority="37">
+    <cfRule type="expression" dxfId="227" priority="37">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="228" priority="38">
+    <cfRule type="expression" dxfId="226" priority="38">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:R55">
-    <cfRule type="expression" dxfId="227" priority="35">
+    <cfRule type="expression" dxfId="225" priority="35">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="226" priority="36">
+    <cfRule type="expression" dxfId="224" priority="36">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:R59">
-    <cfRule type="expression" dxfId="225" priority="33">
+    <cfRule type="expression" dxfId="223" priority="33">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="224" priority="34">
+    <cfRule type="expression" dxfId="222" priority="34">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:R63">
-    <cfRule type="expression" dxfId="223" priority="31">
+    <cfRule type="expression" dxfId="221" priority="32">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="220" priority="31">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="222" priority="32">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:R67">
-    <cfRule type="expression" dxfId="221" priority="29">
+    <cfRule type="expression" dxfId="219" priority="29">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="220" priority="30">
+    <cfRule type="expression" dxfId="218" priority="30">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D71:R71">
-    <cfRule type="expression" dxfId="219" priority="27">
+    <cfRule type="expression" dxfId="217" priority="27">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="218" priority="28">
+    <cfRule type="expression" dxfId="216" priority="28">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:R75">
-    <cfRule type="expression" dxfId="217" priority="25">
+    <cfRule type="expression" dxfId="215" priority="25">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="216" priority="26">
+    <cfRule type="expression" dxfId="214" priority="26">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D79:R79">
-    <cfRule type="expression" dxfId="215" priority="23">
+    <cfRule type="expression" dxfId="213" priority="24">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="212" priority="23">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="214" priority="24">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:R83">
-    <cfRule type="expression" dxfId="213" priority="21">
+    <cfRule type="expression" dxfId="211" priority="22">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="210" priority="21">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="212" priority="22">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:R87">
-    <cfRule type="expression" dxfId="211" priority="19">
+    <cfRule type="expression" dxfId="209" priority="19">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="210" priority="20">
+    <cfRule type="expression" dxfId="208" priority="20">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D91:R91">
-    <cfRule type="expression" dxfId="209" priority="17">
+    <cfRule type="expression" dxfId="207" priority="18">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="206" priority="17">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="208" priority="18">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D95:R95">
-    <cfRule type="expression" dxfId="207" priority="15">
+    <cfRule type="expression" dxfId="205" priority="15">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="206" priority="16">
+    <cfRule type="expression" dxfId="204" priority="16">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D99:R99">
-    <cfRule type="expression" dxfId="205" priority="13">
+    <cfRule type="expression" dxfId="203" priority="14">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="202" priority="13">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="204" priority="14">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D103:R103">
-    <cfRule type="expression" dxfId="203" priority="11">
+    <cfRule type="expression" dxfId="201" priority="12">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="200" priority="11">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="202" priority="12">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:R107">
-    <cfRule type="expression" dxfId="201" priority="9">
+    <cfRule type="expression" dxfId="199" priority="9">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="200" priority="10">
+    <cfRule type="expression" dxfId="198" priority="10">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:R111">
-    <cfRule type="expression" dxfId="199" priority="7">
+    <cfRule type="expression" dxfId="197" priority="8">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="196" priority="7">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="198" priority="8">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:R115">
-    <cfRule type="expression" dxfId="197" priority="5">
+    <cfRule type="expression" dxfId="195" priority="5">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="196" priority="6">
+    <cfRule type="expression" dxfId="194" priority="6">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:R119">
-    <cfRule type="expression" dxfId="195" priority="3">
+    <cfRule type="expression" dxfId="193" priority="3">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="194" priority="4">
+    <cfRule type="expression" dxfId="192" priority="4">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:R123">
-    <cfRule type="expression" dxfId="193" priority="1">
+    <cfRule type="expression" dxfId="191" priority="1">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="192" priority="2">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D127:R127 D3:R3 D131:R131 D135:R135 D139:R139 D143:R143 D147:R147 D151:R151 D155:R155 D159:R159 D163:R163">
-    <cfRule type="expression" dxfId="191" priority="143">
-      <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="190" priority="144">
+    <cfRule type="expression" dxfId="190" priority="2">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D167:R167 D171:R171 D175:R175 D179:R179 D183:R183 D187:R187 D191:R191 D195:R195 D199:R199">
-    <cfRule type="expression" dxfId="189" priority="141">
+    <cfRule type="expression" dxfId="189" priority="142">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="188" priority="141">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="188" priority="142">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D203:R203">
-    <cfRule type="expression" dxfId="187" priority="139">
+    <cfRule type="expression" dxfId="187" priority="140">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="186" priority="139">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="186" priority="140">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D207:R207 D211:R211 D215:R215 D219:R219 D223:R223 D227:R227 D231:R231 D235:R235 D239:R239">
-    <cfRule type="expression" dxfId="185" priority="137">
+    <cfRule type="expression" dxfId="185" priority="138">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="184" priority="137">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="184" priority="138">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D243:R243">
-    <cfRule type="expression" dxfId="183" priority="93">
+    <cfRule type="expression" dxfId="183" priority="94">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="182" priority="93">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="182" priority="94">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D247:R247 D251:R251 D255:R255 D259:R259 D263:R263 D267:R267 D271:R271 D275:R275 D279:R279">
-    <cfRule type="expression" dxfId="181" priority="91">
+    <cfRule type="expression" dxfId="181" priority="92">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="180" priority="91">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="180" priority="92">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D283:R283">
@@ -30014,11 +30021,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D291:R291 D295:R295 D299:R299 D303:R303 D307:R307 D311:R311 D315:R315 D319:R319 D323:R323">
-    <cfRule type="expression" dxfId="175" priority="85">
+    <cfRule type="expression" dxfId="175" priority="86">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="174" priority="85">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="174" priority="86">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D327:R327">
@@ -30046,19 +30053,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D371:R371">
-    <cfRule type="expression" dxfId="167" priority="77">
+    <cfRule type="expression" dxfId="167" priority="78">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="166" priority="77">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="166" priority="78">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D375:R375">
-    <cfRule type="expression" dxfId="165" priority="75">
+    <cfRule type="expression" dxfId="165" priority="76">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="164" priority="75">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="164" priority="76">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D379:R379 D383:R383 D387:R387 D391:R391 D395:R395 D399:R399 D403:R403 D407:R407 D411:R411">
@@ -30070,27 +30077,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D415:R415">
-    <cfRule type="expression" dxfId="161" priority="71">
+    <cfRule type="expression" dxfId="161" priority="72">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="160" priority="71">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="160" priority="72">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D419:R419">
-    <cfRule type="expression" dxfId="159" priority="69">
+    <cfRule type="expression" dxfId="159" priority="70">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="158" priority="69">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="158" priority="70">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D423:R423 D427:R427 D431:R431 D435:R435 D439:R439 D443:R443 D447:R447 D451:R451 D455:R455">
-    <cfRule type="expression" dxfId="157" priority="67">
+    <cfRule type="expression" dxfId="157" priority="68">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="156" priority="67">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="156" priority="68">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D459:R459">
@@ -30270,7 +30277,7 @@
         <v>62</v>
       </c>
       <c r="T3" s="16"/>
-      <c r="V3" s="62" t="s">
+      <c r="V3" s="67" t="s">
         <v>1260</v>
       </c>
     </row>
@@ -30318,7 +30325,7 @@
         <v>62</v>
       </c>
       <c r="S4" s="19"/>
-      <c r="V4" s="63"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="20">
@@ -30370,7 +30377,7 @@
         <v>291</v>
       </c>
       <c r="S5" s="21"/>
-      <c r="V5" s="63"/>
+      <c r="V5" s="65"/>
     </row>
     <row r="6" spans="1:22" s="26" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="22"/>
@@ -30417,7 +30424,7 @@
         <v>62</v>
       </c>
       <c r="S6" s="25"/>
-      <c r="V6" s="63"/>
+      <c r="V6" s="65"/>
     </row>
     <row r="7" spans="1:22" s="30" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="27"/>
@@ -30448,7 +30455,7 @@
       <c r="Q7" s="54"/>
       <c r="R7" s="54"/>
       <c r="S7" s="29"/>
-      <c r="V7" s="63"/>
+      <c r="V7" s="65"/>
     </row>
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="17"/>
@@ -30492,7 +30499,7 @@
         <v>1226</v>
       </c>
       <c r="S8" s="19"/>
-      <c r="V8" s="63"/>
+      <c r="V8" s="65"/>
     </row>
     <row r="9" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="20">
@@ -30546,7 +30553,7 @@
       </c>
       <c r="S9" s="21"/>
       <c r="T9" s="16"/>
-      <c r="V9" s="63"/>
+      <c r="V9" s="65"/>
     </row>
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="22"/>
@@ -30590,7 +30597,7 @@
         <v>399</v>
       </c>
       <c r="S10" s="31"/>
-      <c r="V10" s="63"/>
+      <c r="V10" s="65"/>
     </row>
     <row r="11" spans="1:22" s="29" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="32"/>
@@ -30614,7 +30621,7 @@
       <c r="P11" s="54"/>
       <c r="Q11" s="54"/>
       <c r="R11" s="54"/>
-      <c r="V11" s="63"/>
+      <c r="V11" s="65"/>
     </row>
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="17"/>
@@ -30644,7 +30651,7 @@
       <c r="Q12" s="18"/>
       <c r="R12" s="18"/>
       <c r="S12" s="19"/>
-      <c r="V12" s="63"/>
+      <c r="V12" s="65"/>
     </row>
     <row r="13" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="20">
@@ -30683,7 +30690,7 @@
       <c r="Q13" s="41"/>
       <c r="R13" s="41"/>
       <c r="S13" s="21"/>
-      <c r="V13" s="63"/>
+      <c r="V13" s="65"/>
     </row>
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="22"/>
@@ -30713,7 +30720,7 @@
       <c r="Q14" s="24"/>
       <c r="R14" s="24"/>
       <c r="S14" s="31"/>
-      <c r="V14" s="63"/>
+      <c r="V14" s="65"/>
     </row>
     <row r="15" spans="1:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="12"/>
@@ -30733,7 +30740,7 @@
       <c r="P15" s="54"/>
       <c r="Q15" s="54"/>
       <c r="R15" s="54"/>
-      <c r="V15" s="63"/>
+      <c r="V15" s="65"/>
     </row>
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="17"/>
@@ -30753,7 +30760,7 @@
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
       <c r="S16" s="19"/>
-      <c r="V16" s="63"/>
+      <c r="V16" s="65"/>
     </row>
     <row r="17" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="20">
@@ -30778,7 +30785,7 @@
       <c r="Q17" s="41"/>
       <c r="R17" s="41"/>
       <c r="S17" s="21"/>
-      <c r="V17" s="63"/>
+      <c r="V17" s="65"/>
     </row>
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="22"/>
@@ -30798,7 +30805,7 @@
       <c r="Q18" s="24"/>
       <c r="R18" s="24"/>
       <c r="S18" s="31"/>
-      <c r="V18" s="63"/>
+      <c r="V18" s="65"/>
     </row>
     <row r="19" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="12"/>
@@ -30840,7 +30847,7 @@
       <c r="R19" s="54" t="s">
         <v>1177</v>
       </c>
-      <c r="V19" s="63"/>
+      <c r="V19" s="65"/>
     </row>
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="17"/>
@@ -30888,7 +30895,7 @@
         <v>1177</v>
       </c>
       <c r="S20" s="19"/>
-      <c r="V20" s="63"/>
+      <c r="V20" s="65"/>
     </row>
     <row r="21" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="20">
@@ -30941,7 +30948,7 @@
         <v>185</v>
       </c>
       <c r="S21" s="21"/>
-      <c r="V21" s="63"/>
+      <c r="V21" s="65"/>
     </row>
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="22"/>
@@ -30989,7 +30996,7 @@
         <v>1294</v>
       </c>
       <c r="S22" s="31"/>
-      <c r="V22" s="63"/>
+      <c r="V22" s="65"/>
     </row>
     <row r="23" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="12"/>
@@ -31009,7 +31016,7 @@
       <c r="P23" s="54"/>
       <c r="Q23" s="54"/>
       <c r="R23" s="54"/>
-      <c r="V23" s="63"/>
+      <c r="V23" s="65"/>
     </row>
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="17"/>
@@ -31029,7 +31036,7 @@
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
       <c r="S24" s="19"/>
-      <c r="V24" s="63"/>
+      <c r="V24" s="65"/>
     </row>
     <row r="25" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B25" s="20">
@@ -31056,7 +31063,7 @@
       <c r="Q25" s="41"/>
       <c r="R25" s="41"/>
       <c r="S25" s="21"/>
-      <c r="V25" s="63"/>
+      <c r="V25" s="65"/>
     </row>
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="22"/>
@@ -31076,7 +31083,7 @@
       <c r="Q26" s="24"/>
       <c r="R26" s="24"/>
       <c r="S26" s="31"/>
-      <c r="V26" s="63"/>
+      <c r="V26" s="65"/>
     </row>
     <row r="27" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B27" s="12"/>
@@ -31100,7 +31107,7 @@
         <f t="shared" ref="U27:U32" si="1" xml:space="preserve"> MID($N$26,4,1)</f>
         <v/>
       </c>
-      <c r="V27" s="63"/>
+      <c r="V27" s="65"/>
     </row>
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="17"/>
@@ -31124,7 +31131,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V28" s="63"/>
+      <c r="V28" s="65"/>
     </row>
     <row r="29" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B29" s="20">
@@ -31153,7 +31160,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V29" s="63"/>
+      <c r="V29" s="65"/>
     </row>
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="22"/>
@@ -31177,7 +31184,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V30" s="63"/>
+      <c r="V30" s="65"/>
     </row>
     <row r="31" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B31" s="12"/>
@@ -31217,7 +31224,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V31" s="63"/>
+      <c r="V31" s="65"/>
     </row>
     <row r="32" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="17"/>
@@ -31267,7 +31274,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V32" s="63"/>
+      <c r="V32" s="65"/>
     </row>
     <row r="33" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B33" s="20">
@@ -31320,7 +31327,7 @@
         <v>164</v>
       </c>
       <c r="S33" s="21"/>
-      <c r="V33" s="63"/>
+      <c r="V33" s="65"/>
     </row>
     <row r="34" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="22"/>
@@ -31366,7 +31373,7 @@
         <v>1291</v>
       </c>
       <c r="S34" s="31"/>
-      <c r="V34" s="63"/>
+      <c r="V34" s="65"/>
     </row>
     <row r="35" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B35" s="12"/>
@@ -31392,7 +31399,7 @@
       <c r="P35" s="54"/>
       <c r="Q35" s="54"/>
       <c r="R35" s="54"/>
-      <c r="V35" s="63"/>
+      <c r="V35" s="65"/>
     </row>
     <row r="36" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="17"/>
@@ -31418,7 +31425,7 @@
       <c r="Q36" s="18"/>
       <c r="R36" s="18"/>
       <c r="S36" s="19"/>
-      <c r="V36" s="63"/>
+      <c r="V36" s="65"/>
     </row>
     <row r="37" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B37" s="20">
@@ -31455,7 +31462,7 @@
       <c r="Q37" s="41"/>
       <c r="R37" s="41"/>
       <c r="S37" s="21"/>
-      <c r="V37" s="63"/>
+      <c r="V37" s="65"/>
     </row>
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="22"/>
@@ -31481,7 +31488,7 @@
       <c r="Q38" s="24"/>
       <c r="R38" s="24"/>
       <c r="S38" s="31"/>
-      <c r="V38" s="63"/>
+      <c r="V38" s="65"/>
     </row>
     <row r="39" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B39" s="12"/>
@@ -31501,7 +31508,7 @@
       <c r="P39" s="54"/>
       <c r="Q39" s="54"/>
       <c r="R39" s="54"/>
-      <c r="V39" s="63"/>
+      <c r="V39" s="65"/>
     </row>
     <row r="40" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="17"/>
@@ -31521,7 +31528,7 @@
       <c r="Q40" s="18"/>
       <c r="R40" s="18"/>
       <c r="S40" s="19"/>
-      <c r="V40" s="63"/>
+      <c r="V40" s="65"/>
     </row>
     <row r="41" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B41" s="20">
@@ -31546,7 +31553,7 @@
       <c r="Q41" s="41"/>
       <c r="R41" s="41"/>
       <c r="S41" s="21"/>
-      <c r="V41" s="63"/>
+      <c r="V41" s="65"/>
     </row>
     <row r="42" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="22"/>
@@ -31566,7 +31573,7 @@
       <c r="Q42" s="24"/>
       <c r="R42" s="24"/>
       <c r="S42" s="31"/>
-      <c r="V42" s="63"/>
+      <c r="V42" s="65"/>
     </row>
     <row r="43" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B43" s="12"/>
@@ -31594,7 +31601,7 @@
         <v>1276</v>
       </c>
       <c r="R43" s="54"/>
-      <c r="V43" s="63"/>
+      <c r="V43" s="65"/>
     </row>
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="17"/>
@@ -31640,7 +31647,7 @@
         <v>1268</v>
       </c>
       <c r="S44" s="19"/>
-      <c r="V44" s="63"/>
+      <c r="V44" s="65"/>
     </row>
     <row r="45" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B45" s="20">
@@ -31693,7 +31700,7 @@
         <v>1193</v>
       </c>
       <c r="S45" s="21"/>
-      <c r="V45" s="63"/>
+      <c r="V45" s="65"/>
     </row>
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="22"/>
@@ -31739,7 +31746,7 @@
         <v>1340</v>
       </c>
       <c r="S46" s="31"/>
-      <c r="V46" s="63"/>
+      <c r="V46" s="65"/>
     </row>
     <row r="47" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B47" s="12"/>
@@ -31765,7 +31772,7 @@
       <c r="P47" s="54"/>
       <c r="Q47" s="54"/>
       <c r="R47" s="54"/>
-      <c r="V47" s="63"/>
+      <c r="V47" s="65"/>
     </row>
     <row r="48" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="17"/>
@@ -31791,7 +31798,7 @@
       <c r="Q48" s="18"/>
       <c r="R48" s="18"/>
       <c r="S48" s="19"/>
-      <c r="V48" s="63"/>
+      <c r="V48" s="65"/>
     </row>
     <row r="49" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B49" s="20">
@@ -31824,7 +31831,7 @@
       <c r="Q49" s="41"/>
       <c r="R49" s="41"/>
       <c r="S49" s="21"/>
-      <c r="V49" s="63"/>
+      <c r="V49" s="65"/>
     </row>
     <row r="50" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="22"/>
@@ -31850,7 +31857,7 @@
       <c r="Q50" s="24"/>
       <c r="R50" s="24"/>
       <c r="S50" s="31"/>
-      <c r="V50" s="63"/>
+      <c r="V50" s="65"/>
     </row>
     <row r="51" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B51" s="12"/>
@@ -31870,7 +31877,7 @@
       <c r="P51" s="54"/>
       <c r="Q51" s="54"/>
       <c r="R51" s="54"/>
-      <c r="V51" s="63"/>
+      <c r="V51" s="65"/>
     </row>
     <row r="52" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="17"/>
@@ -31890,7 +31897,7 @@
       <c r="Q52" s="18"/>
       <c r="R52" s="18"/>
       <c r="S52" s="19"/>
-      <c r="V52" s="63"/>
+      <c r="V52" s="65"/>
     </row>
     <row r="53" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B53" s="20">
@@ -31915,7 +31922,7 @@
       <c r="Q53" s="41"/>
       <c r="R53" s="41"/>
       <c r="S53" s="21"/>
-      <c r="V53" s="63"/>
+      <c r="V53" s="65"/>
     </row>
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="22"/>
@@ -31935,7 +31942,7 @@
       <c r="Q54" s="24"/>
       <c r="R54" s="24"/>
       <c r="S54" s="31"/>
-      <c r="V54" s="63"/>
+      <c r="V54" s="65"/>
     </row>
     <row r="55" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B55" s="12"/>
@@ -31967,7 +31974,7 @@
       </c>
       <c r="Q55" s="54"/>
       <c r="R55" s="54"/>
-      <c r="V55" s="63"/>
+      <c r="V55" s="65"/>
     </row>
     <row r="56" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="17"/>
@@ -32013,7 +32020,7 @@
         <v>57</v>
       </c>
       <c r="S56" s="19"/>
-      <c r="V56" s="63"/>
+      <c r="V56" s="65"/>
     </row>
     <row r="57" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B57" s="20">
@@ -32066,7 +32073,7 @@
         <v>164</v>
       </c>
       <c r="S57" s="21"/>
-      <c r="V57" s="63"/>
+      <c r="V57" s="65"/>
     </row>
     <row r="58" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="22"/>
@@ -32112,7 +32119,7 @@
         <v>1291</v>
       </c>
       <c r="S58" s="31"/>
-      <c r="V58" s="63"/>
+      <c r="V58" s="65"/>
     </row>
     <row r="59" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B59" s="12"/>
@@ -32134,7 +32141,7 @@
       <c r="P59" s="54"/>
       <c r="Q59" s="54"/>
       <c r="R59" s="54"/>
-      <c r="V59" s="63"/>
+      <c r="V59" s="65"/>
     </row>
     <row r="60" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="17"/>
@@ -32160,7 +32167,7 @@
       <c r="Q60" s="18"/>
       <c r="R60" s="18"/>
       <c r="S60" s="19"/>
-      <c r="V60" s="63"/>
+      <c r="V60" s="65"/>
     </row>
     <row r="61" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B61" s="20">
@@ -32193,7 +32200,7 @@
       <c r="Q61" s="41"/>
       <c r="R61" s="41"/>
       <c r="S61" s="21"/>
-      <c r="V61" s="63"/>
+      <c r="V61" s="65"/>
     </row>
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="22"/>
@@ -32219,7 +32226,7 @@
       <c r="Q62" s="24"/>
       <c r="R62" s="24"/>
       <c r="S62" s="31"/>
-      <c r="V62" s="63"/>
+      <c r="V62" s="65"/>
     </row>
     <row r="63" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B63" s="12"/>
@@ -32239,7 +32246,7 @@
       <c r="P63" s="54"/>
       <c r="Q63" s="54"/>
       <c r="R63" s="54"/>
-      <c r="V63" s="63"/>
+      <c r="V63" s="65"/>
     </row>
     <row r="64" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B64" s="17"/>
@@ -32259,7 +32266,7 @@
       <c r="Q64" s="18"/>
       <c r="R64" s="18"/>
       <c r="S64" s="19"/>
-      <c r="V64" s="63"/>
+      <c r="V64" s="65"/>
     </row>
     <row r="65" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B65" s="20">
@@ -32282,7 +32289,7 @@
       <c r="Q65" s="41"/>
       <c r="R65" s="41"/>
       <c r="S65" s="21"/>
-      <c r="V65" s="63"/>
+      <c r="V65" s="65"/>
     </row>
     <row r="66" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="22"/>
@@ -32302,7 +32309,7 @@
       <c r="Q66" s="24"/>
       <c r="R66" s="24"/>
       <c r="S66" s="31"/>
-      <c r="V66" s="63"/>
+      <c r="V66" s="65"/>
     </row>
     <row r="67" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B67" s="12"/>
@@ -32322,7 +32329,7 @@
       <c r="P67" s="54"/>
       <c r="Q67" s="54"/>
       <c r="R67" s="54"/>
-      <c r="V67" s="63"/>
+      <c r="V67" s="65"/>
     </row>
     <row r="68" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="17"/>
@@ -32342,7 +32349,7 @@
       <c r="Q68" s="18"/>
       <c r="R68" s="18"/>
       <c r="S68" s="19"/>
-      <c r="V68" s="63"/>
+      <c r="V68" s="65"/>
     </row>
     <row r="69" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B69" s="20">
@@ -32365,7 +32372,7 @@
       <c r="Q69" s="41"/>
       <c r="R69" s="41"/>
       <c r="S69" s="21"/>
-      <c r="V69" s="63"/>
+      <c r="V69" s="65"/>
     </row>
     <row r="70" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="22"/>
@@ -32385,7 +32392,7 @@
       <c r="Q70" s="24"/>
       <c r="R70" s="24"/>
       <c r="S70" s="31"/>
-      <c r="V70" s="63"/>
+      <c r="V70" s="65"/>
     </row>
     <row r="71" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B71" s="12"/>
@@ -32405,7 +32412,7 @@
       <c r="P71" s="54"/>
       <c r="Q71" s="54"/>
       <c r="R71" s="54"/>
-      <c r="V71" s="63"/>
+      <c r="V71" s="65"/>
     </row>
     <row r="72" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="17"/>
@@ -32425,7 +32432,7 @@
       <c r="Q72" s="18"/>
       <c r="R72" s="18"/>
       <c r="S72" s="19"/>
-      <c r="V72" s="63"/>
+      <c r="V72" s="65"/>
     </row>
     <row r="73" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B73" s="20">
@@ -32448,7 +32455,7 @@
       <c r="Q73" s="41"/>
       <c r="R73" s="41"/>
       <c r="S73" s="21"/>
-      <c r="V73" s="63"/>
+      <c r="V73" s="65"/>
     </row>
     <row r="74" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="22"/>
@@ -32468,7 +32475,7 @@
       <c r="Q74" s="24"/>
       <c r="R74" s="24"/>
       <c r="S74" s="31"/>
-      <c r="V74" s="63"/>
+      <c r="V74" s="65"/>
     </row>
     <row r="75" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B75" s="12"/>
@@ -32488,7 +32495,7 @@
       <c r="P75" s="54"/>
       <c r="Q75" s="54"/>
       <c r="R75" s="54"/>
-      <c r="V75" s="63"/>
+      <c r="V75" s="65"/>
     </row>
     <row r="76" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="17"/>
@@ -32508,7 +32515,7 @@
       <c r="Q76" s="18"/>
       <c r="R76" s="18"/>
       <c r="S76" s="19"/>
-      <c r="V76" s="63"/>
+      <c r="V76" s="65"/>
     </row>
     <row r="77" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B77" s="20">
@@ -32531,7 +32538,7 @@
       <c r="Q77" s="41"/>
       <c r="R77" s="41"/>
       <c r="S77" s="21"/>
-      <c r="V77" s="63"/>
+      <c r="V77" s="65"/>
     </row>
     <row r="78" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="22"/>
@@ -32551,7 +32558,7 @@
       <c r="Q78" s="24"/>
       <c r="R78" s="24"/>
       <c r="S78" s="31"/>
-      <c r="V78" s="63"/>
+      <c r="V78" s="65"/>
     </row>
     <row r="79" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B79" s="12"/>
@@ -32571,7 +32578,7 @@
       <c r="P79" s="54"/>
       <c r="Q79" s="54"/>
       <c r="R79" s="54"/>
-      <c r="V79" s="63"/>
+      <c r="V79" s="65"/>
     </row>
     <row r="80" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="17"/>
@@ -32591,7 +32598,7 @@
       <c r="Q80" s="18"/>
       <c r="R80" s="18"/>
       <c r="S80" s="19"/>
-      <c r="V80" s="63"/>
+      <c r="V80" s="65"/>
     </row>
     <row r="81" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B81" s="20">
@@ -32614,7 +32621,7 @@
       <c r="Q81" s="41"/>
       <c r="R81" s="41"/>
       <c r="S81" s="21"/>
-      <c r="V81" s="63"/>
+      <c r="V81" s="65"/>
     </row>
     <row r="82" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="22"/>
@@ -32634,7 +32641,7 @@
       <c r="Q82" s="24"/>
       <c r="R82" s="24"/>
       <c r="S82" s="31"/>
-      <c r="V82" s="64"/>
+      <c r="V82" s="66"/>
     </row>
     <row r="83" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B83" s="12"/>
@@ -40626,19 +40633,19 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D3:R3">
-    <cfRule type="expression" dxfId="149" priority="93">
+    <cfRule type="expression" dxfId="149" priority="94">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="148" priority="93">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="148" priority="94">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7:R7">
-    <cfRule type="expression" dxfId="147" priority="57">
+    <cfRule type="expression" dxfId="147" priority="58">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="146" priority="57">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="146" priority="58">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:R11">
@@ -40650,11 +40657,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:R15">
-    <cfRule type="expression" dxfId="143" priority="53">
+    <cfRule type="expression" dxfId="143" priority="54">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="142" priority="53">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="142" priority="54">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:R19">
@@ -40682,35 +40689,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D31:R31">
-    <cfRule type="expression" dxfId="135" priority="45">
+    <cfRule type="expression" dxfId="135" priority="46">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="134" priority="45">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="134" priority="46">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35:R35">
-    <cfRule type="expression" dxfId="133" priority="43">
+    <cfRule type="expression" dxfId="133" priority="44">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="132" priority="43">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="132" priority="44">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:R39">
-    <cfRule type="expression" dxfId="131" priority="41">
+    <cfRule type="expression" dxfId="131" priority="42">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="130" priority="41">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="130" priority="42">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:R43">
-    <cfRule type="expression" dxfId="129" priority="39">
+    <cfRule type="expression" dxfId="129" priority="40">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="128" priority="39">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="128" priority="40">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:R47">
@@ -40746,11 +40753,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:R63">
-    <cfRule type="expression" dxfId="119" priority="29">
+    <cfRule type="expression" dxfId="119" priority="30">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="118" priority="29">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="118" priority="30">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:R67">
@@ -40770,19 +40777,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:R75">
-    <cfRule type="expression" dxfId="113" priority="23">
+    <cfRule type="expression" dxfId="113" priority="24">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="112" priority="23">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="112" priority="24">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D79:R79">
-    <cfRule type="expression" dxfId="111" priority="21">
+    <cfRule type="expression" dxfId="111" priority="22">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="110" priority="21">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="110" priority="22">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:R83">
@@ -40810,11 +40817,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D95:R95">
-    <cfRule type="expression" dxfId="103" priority="13">
+    <cfRule type="expression" dxfId="103" priority="14">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="13">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="14">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D99:R99">
@@ -40826,19 +40833,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D103:R103">
-    <cfRule type="expression" dxfId="99" priority="9">
+    <cfRule type="expression" dxfId="99" priority="10">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="9">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="98" priority="10">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:R107">
-    <cfRule type="expression" dxfId="97" priority="7">
+    <cfRule type="expression" dxfId="97" priority="8">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="7">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="96" priority="8">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:R111">
@@ -40866,43 +40873,43 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:R123 D127:R127 D131:R131 D135:R135 D139:R139 D143:R143 D147:R147 D151:R151 D155:R155 D159:R159 D163:R163">
-    <cfRule type="expression" dxfId="89" priority="101">
+    <cfRule type="expression" dxfId="89" priority="102">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="101">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="102">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D167:R167 D171:R171 D175:R175 D179:R179 D183:R183 D187:R187 D191:R191 D195:R195 D199:R199">
-    <cfRule type="expression" dxfId="87" priority="99">
+    <cfRule type="expression" dxfId="87" priority="100">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="99">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="100">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D203:R203">
-    <cfRule type="expression" dxfId="85" priority="97">
+    <cfRule type="expression" dxfId="85" priority="98">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="97">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="98">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D207:R207 D211:R211 D215:R215 D219:R219 D223:R223 D227:R227 D231:R231 D235:R235 D239:R239">
-    <cfRule type="expression" dxfId="83" priority="95">
+    <cfRule type="expression" dxfId="83" priority="96">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="95">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="96">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D243:R243">
-    <cfRule type="expression" dxfId="81" priority="91">
+    <cfRule type="expression" dxfId="81" priority="92">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="91">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="92">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D247:R247 D251:R251 D255:R255 D259:R259 D263:R263 D267:R267 D271:R271 D275:R275 D279:R279">
@@ -40970,43 +40977,43 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D375:R375">
-    <cfRule type="expression" dxfId="63" priority="73">
+    <cfRule type="expression" dxfId="63" priority="74">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="73">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="74">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D379:R379 D383:R383 D387:R387 D391:R391 D395:R395 D399:R399 D403:R403 D407:R407 D411:R411">
-    <cfRule type="expression" dxfId="61" priority="71">
+    <cfRule type="expression" dxfId="61" priority="72">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="60" priority="71">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="72">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D415:R415">
-    <cfRule type="expression" dxfId="59" priority="69">
+    <cfRule type="expression" dxfId="59" priority="70">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="69">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="70">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D419:R419">
-    <cfRule type="expression" dxfId="57" priority="67">
+    <cfRule type="expression" dxfId="57" priority="68">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="67">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="68">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D423:R423 D427:R427 D431:R431 D435:R435 D439:R439 D443:R443 D447:R447 D451:R451 D455:R455">
-    <cfRule type="expression" dxfId="55" priority="65">
+    <cfRule type="expression" dxfId="55" priority="66">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="65">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="66">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D459:R459">
@@ -41170,7 +41177,7 @@
       <c r="Q3" s="14"/>
       <c r="R3" s="14"/>
       <c r="T3" s="16"/>
-      <c r="V3" s="62" t="s">
+      <c r="V3" s="67" t="s">
         <v>66</v>
       </c>
     </row>
@@ -41218,7 +41225,7 @@
       </c>
       <c r="R4" s="18"/>
       <c r="S4" s="19"/>
-      <c r="V4" s="65"/>
+      <c r="V4" s="68"/>
     </row>
     <row r="5" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="20">
@@ -41270,7 +41277,7 @@
         <v>30</v>
       </c>
       <c r="S5" s="21"/>
-      <c r="V5" s="65"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:22" s="26" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="22"/>
@@ -41317,7 +41324,7 @@
       </c>
       <c r="R6" s="24"/>
       <c r="S6" s="25"/>
-      <c r="V6" s="65"/>
+      <c r="V6" s="68"/>
     </row>
     <row r="7" spans="1:22" s="30" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="27"/>
@@ -41338,7 +41345,7 @@
       <c r="Q7" s="14"/>
       <c r="R7" s="14"/>
       <c r="S7" s="29"/>
-      <c r="V7" s="65"/>
+      <c r="V7" s="68"/>
     </row>
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="17"/>
@@ -41382,7 +41389,7 @@
         <v>553</v>
       </c>
       <c r="S8" s="19"/>
-      <c r="V8" s="65"/>
+      <c r="V8" s="68"/>
     </row>
     <row r="9" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="20">
@@ -41436,7 +41443,7 @@
       </c>
       <c r="S9" s="21"/>
       <c r="T9" s="16"/>
-      <c r="V9" s="65"/>
+      <c r="V9" s="68"/>
     </row>
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="22"/>
@@ -41480,7 +41487,7 @@
         <v>554</v>
       </c>
       <c r="S10" s="31"/>
-      <c r="V10" s="65"/>
+      <c r="V10" s="68"/>
     </row>
     <row r="11" spans="1:22" s="29" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="32"/>
@@ -41500,7 +41507,7 @@
       <c r="P11" s="14"/>
       <c r="Q11" s="14"/>
       <c r="R11" s="14"/>
-      <c r="V11" s="65"/>
+      <c r="V11" s="68"/>
     </row>
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="17"/>
@@ -41546,7 +41553,7 @@
         <v>579</v>
       </c>
       <c r="S12" s="19"/>
-      <c r="V12" s="65"/>
+      <c r="V12" s="68"/>
     </row>
     <row r="13" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="20">
@@ -41599,7 +41606,7 @@
         <v>99</v>
       </c>
       <c r="S13" s="21"/>
-      <c r="V13" s="65"/>
+      <c r="V13" s="68"/>
     </row>
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="22"/>
@@ -41645,7 +41652,7 @@
         <v>580</v>
       </c>
       <c r="S14" s="31"/>
-      <c r="V14" s="65"/>
+      <c r="V14" s="68"/>
     </row>
     <row r="15" spans="1:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="12"/>
@@ -41665,7 +41672,7 @@
       <c r="P15" s="14"/>
       <c r="Q15" s="14"/>
       <c r="R15" s="14"/>
-      <c r="V15" s="65"/>
+      <c r="V15" s="68"/>
     </row>
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="17"/>
@@ -41711,7 +41718,7 @@
       </c>
       <c r="R16" s="18"/>
       <c r="S16" s="19"/>
-      <c r="V16" s="65"/>
+      <c r="V16" s="68"/>
     </row>
     <row r="17" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="20">
@@ -41764,7 +41771,7 @@
         <v>30</v>
       </c>
       <c r="S17" s="21"/>
-      <c r="V17" s="65"/>
+      <c r="V17" s="68"/>
     </row>
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="22"/>
@@ -41810,7 +41817,7 @@
       </c>
       <c r="R18" s="24"/>
       <c r="S18" s="31"/>
-      <c r="V18" s="65"/>
+      <c r="V18" s="68"/>
     </row>
     <row r="19" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="12"/>
@@ -41830,7 +41837,7 @@
       <c r="P19" s="14"/>
       <c r="Q19" s="14"/>
       <c r="R19" s="14"/>
-      <c r="V19" s="65"/>
+      <c r="V19" s="68"/>
     </row>
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="17"/>
@@ -41850,7 +41857,7 @@
       <c r="Q20" s="18"/>
       <c r="R20" s="18"/>
       <c r="S20" s="19"/>
-      <c r="V20" s="65"/>
+      <c r="V20" s="68"/>
     </row>
     <row r="21" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="20">
@@ -41877,7 +41884,7 @@
       <c r="Q21" s="41"/>
       <c r="R21" s="41"/>
       <c r="S21" s="21"/>
-      <c r="V21" s="65"/>
+      <c r="V21" s="68"/>
     </row>
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="22"/>
@@ -41897,7 +41904,7 @@
       <c r="Q22" s="24"/>
       <c r="R22" s="24"/>
       <c r="S22" s="31"/>
-      <c r="V22" s="66"/>
+      <c r="V22" s="69"/>
     </row>
     <row r="23" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="12"/>
@@ -48444,43 +48451,43 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:R11">
-    <cfRule type="expression" dxfId="43" priority="39">
+    <cfRule type="expression" dxfId="43" priority="40">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="39">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="40">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:R15">
-    <cfRule type="expression" dxfId="41" priority="37">
+    <cfRule type="expression" dxfId="41" priority="38">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="37">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="38">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:R19">
-    <cfRule type="expression" dxfId="39" priority="35">
+    <cfRule type="expression" dxfId="39" priority="36">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="35">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="36">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23:R23 D39:R39 D87:R87 D91:R91 D95:R95 D99:R99 D103:R103 D111:R111 D115:R115 D119:R119 D123:R123 D127:R127 D131:R131 D135:R135 D139:R139 D143:R143 D147:R147 D151:R151 D155:R155 D159:R159 D163:R163">
-    <cfRule type="expression" dxfId="37" priority="47">
+    <cfRule type="expression" dxfId="37" priority="48">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="47">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="48">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27:R27">
-    <cfRule type="expression" dxfId="35" priority="33">
+    <cfRule type="expression" dxfId="35" priority="34">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="33">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D31:R31">
@@ -48492,19 +48499,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35:R35">
-    <cfRule type="expression" dxfId="31" priority="29">
+    <cfRule type="expression" dxfId="31" priority="30">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="29">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="30">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:R43">
-    <cfRule type="expression" dxfId="29" priority="27">
+    <cfRule type="expression" dxfId="29" priority="28">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="27">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="28">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:R47">
@@ -48516,19 +48523,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:R51">
-    <cfRule type="expression" dxfId="25" priority="23">
+    <cfRule type="expression" dxfId="25" priority="24">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="23">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="24">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:R55">
-    <cfRule type="expression" dxfId="23" priority="21">
+    <cfRule type="expression" dxfId="23" priority="22">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="21">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:R59">
@@ -48540,35 +48547,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:R63">
-    <cfRule type="expression" dxfId="19" priority="17">
+    <cfRule type="expression" dxfId="19" priority="18">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="17">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:R67">
-    <cfRule type="expression" dxfId="17" priority="15">
+    <cfRule type="expression" dxfId="17" priority="16">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="15">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="16">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D71:R71">
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="15" priority="14">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="13">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:R75">
-    <cfRule type="expression" dxfId="13" priority="11">
+    <cfRule type="expression" dxfId="13" priority="12">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="11">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="12">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D79:R79">
@@ -48580,11 +48587,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:R83">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="9" priority="8">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="7">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:R107">
